--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>267.381</v>
+        <v>239.905</v>
       </c>
       <c r="D2">
-        <v>5.522</v>
+        <v>4.832</v>
       </c>
       <c r="E2">
-        <v>2.35</v>
+        <v>2.198</v>
       </c>
       <c r="F2">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2">
-        <v>262.866</v>
+        <v>235.656</v>
       </c>
       <c r="H2">
-        <v>272.077</v>
+        <v>244.273</v>
       </c>
       <c r="I2">
-        <v>262.679</v>
+        <v>235.629</v>
       </c>
       <c r="J2">
-        <v>271.864</v>
+        <v>243.948</v>
       </c>
       <c r="K2">
-        <v>262.988</v>
+        <v>235.922</v>
       </c>
       <c r="L2">
-        <v>272.174</v>
+        <v>244.241</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>177.567</v>
+        <v>159.44</v>
       </c>
       <c r="D3">
-        <v>3.133</v>
+        <v>2.608</v>
       </c>
       <c r="E3">
-        <v>1.77</v>
+        <v>1.615</v>
       </c>
       <c r="F3">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="G3">
-        <v>174.102</v>
+        <v>156.2</v>
       </c>
       <c r="H3">
-        <v>181.04</v>
+        <v>162.53</v>
       </c>
       <c r="I3">
-        <v>173.956</v>
+        <v>156.071</v>
       </c>
       <c r="J3">
-        <v>181.044</v>
+        <v>162.445</v>
       </c>
       <c r="K3">
-        <v>174.093</v>
+        <v>156.359</v>
       </c>
       <c r="L3">
-        <v>181.181</v>
+        <v>162.734</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>122.467</v>
+        <v>105.234</v>
       </c>
       <c r="D4">
-        <v>2.554</v>
+        <v>2.016</v>
       </c>
       <c r="E4">
-        <v>1.598</v>
+        <v>1.42</v>
       </c>
       <c r="F4">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
       <c r="G4">
-        <v>119.351</v>
+        <v>102.367</v>
       </c>
       <c r="H4">
-        <v>125.616</v>
+        <v>107.933</v>
       </c>
       <c r="I4">
-        <v>119.153</v>
+        <v>102.418</v>
       </c>
       <c r="J4">
-        <v>125.485</v>
+        <v>107.952</v>
       </c>
       <c r="K4">
-        <v>119.465</v>
+        <v>102.433</v>
       </c>
       <c r="L4">
-        <v>125.798</v>
+        <v>107.966</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>90.712</v>
+        <v>74.93300000000001</v>
       </c>
       <c r="D5">
-        <v>3.741</v>
+        <v>2.466</v>
       </c>
       <c r="E5">
-        <v>1.934</v>
+        <v>1.57</v>
       </c>
       <c r="F5">
-        <v>0.061</v>
+        <v>0.05</v>
       </c>
       <c r="G5">
-        <v>86.93300000000001</v>
+        <v>71.703</v>
       </c>
       <c r="H5">
-        <v>94.515</v>
+        <v>77.85899999999999</v>
       </c>
       <c r="I5">
-        <v>86.437</v>
+        <v>71.495</v>
       </c>
       <c r="J5">
-        <v>94.245</v>
+        <v>77.654</v>
       </c>
       <c r="K5">
-        <v>87.191</v>
+        <v>72.06100000000001</v>
       </c>
       <c r="L5">
-        <v>95</v>
+        <v>78.21899999999999</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>75.324</v>
+        <v>57.501</v>
       </c>
       <c r="D6">
-        <v>1.653</v>
+        <v>0.931</v>
       </c>
       <c r="E6">
-        <v>1.286</v>
+        <v>0.965</v>
       </c>
       <c r="F6">
-        <v>0.041</v>
+        <v>0.031</v>
       </c>
       <c r="G6">
-        <v>72.86</v>
+        <v>55.659</v>
       </c>
       <c r="H6">
-        <v>77.899</v>
+        <v>59.442</v>
       </c>
       <c r="I6">
-        <v>72.694</v>
+        <v>55.659</v>
       </c>
       <c r="J6">
-        <v>77.798</v>
+        <v>59.439</v>
       </c>
       <c r="K6">
-        <v>72.90600000000001</v>
+        <v>55.613</v>
       </c>
       <c r="L6">
-        <v>78.01000000000001</v>
+        <v>59.393</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>64.363</v>
+        <v>46.776</v>
       </c>
       <c r="D7">
-        <v>1.515</v>
+        <v>0.819</v>
       </c>
       <c r="E7">
-        <v>1.231</v>
+        <v>0.905</v>
       </c>
       <c r="F7">
-        <v>0.039</v>
+        <v>0.029</v>
       </c>
       <c r="G7">
-        <v>61.901</v>
+        <v>45.02</v>
       </c>
       <c r="H7">
-        <v>66.72499999999999</v>
+        <v>48.568</v>
       </c>
       <c r="I7">
-        <v>61.864</v>
+        <v>45.037</v>
       </c>
       <c r="J7">
-        <v>66.70399999999999</v>
+        <v>48.489</v>
       </c>
       <c r="K7">
-        <v>61.971</v>
+        <v>45.08</v>
       </c>
       <c r="L7">
-        <v>66.812</v>
+        <v>48.533</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>57.66</v>
+        <v>40.338</v>
       </c>
       <c r="D8">
-        <v>1.466</v>
+        <v>0.71</v>
       </c>
       <c r="E8">
-        <v>1.211</v>
+        <v>0.843</v>
       </c>
       <c r="F8">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="G8">
-        <v>55.308</v>
+        <v>38.724</v>
       </c>
       <c r="H8">
-        <v>60.054</v>
+        <v>42.028</v>
       </c>
       <c r="I8">
-        <v>55.281</v>
+        <v>38.643</v>
       </c>
       <c r="J8">
-        <v>60.03</v>
+        <v>42.007</v>
       </c>
       <c r="K8">
-        <v>55.311</v>
+        <v>38.707</v>
       </c>
       <c r="L8">
-        <v>60.059</v>
+        <v>42.071</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>51.72</v>
+        <v>34.879</v>
       </c>
       <c r="D9">
-        <v>1.243</v>
+        <v>0.621</v>
       </c>
       <c r="E9">
-        <v>1.115</v>
+        <v>0.788</v>
       </c>
       <c r="F9">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="G9">
-        <v>49.443</v>
+        <v>33.312</v>
       </c>
       <c r="H9">
-        <v>53.813</v>
+        <v>36.401</v>
       </c>
       <c r="I9">
-        <v>49.458</v>
+        <v>33.244</v>
       </c>
       <c r="J9">
-        <v>53.95</v>
+        <v>36.395</v>
       </c>
       <c r="K9">
-        <v>49.399</v>
+        <v>33.341</v>
       </c>
       <c r="L9">
-        <v>53.89</v>
+        <v>36.491</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>47.995</v>
+        <v>31.263</v>
       </c>
       <c r="D10">
-        <v>1.108</v>
+        <v>0.538</v>
       </c>
       <c r="E10">
-        <v>1.053</v>
+        <v>0.734</v>
       </c>
       <c r="F10">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="G10">
-        <v>45.838</v>
+        <v>29.811</v>
       </c>
       <c r="H10">
-        <v>49.963</v>
+        <v>32.687</v>
       </c>
       <c r="I10">
-        <v>45.807</v>
+        <v>29.799</v>
       </c>
       <c r="J10">
-        <v>49.917</v>
+        <v>32.689</v>
       </c>
       <c r="K10">
-        <v>45.979</v>
+        <v>29.822</v>
       </c>
       <c r="L10">
-        <v>50.088</v>
+        <v>32.712</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>47.67</v>
+        <v>30.158</v>
       </c>
       <c r="D11">
-        <v>1.131</v>
+        <v>0.492</v>
       </c>
       <c r="E11">
-        <v>1.063</v>
+        <v>0.701</v>
       </c>
       <c r="F11">
-        <v>0.034</v>
+        <v>0.022</v>
       </c>
       <c r="G11">
-        <v>45.521</v>
+        <v>28.76</v>
       </c>
       <c r="H11">
-        <v>49.689</v>
+        <v>31.508</v>
       </c>
       <c r="I11">
-        <v>45.332</v>
+        <v>28.732</v>
       </c>
       <c r="J11">
-        <v>49.715</v>
+        <v>31.471</v>
       </c>
       <c r="K11">
-        <v>45.56</v>
+        <v>28.821</v>
       </c>
       <c r="L11">
-        <v>49.943</v>
+        <v>31.56</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>45.807</v>
+        <v>28.092</v>
       </c>
       <c r="D12">
-        <v>1.309</v>
+        <v>0.555</v>
       </c>
       <c r="E12">
-        <v>1.144</v>
+        <v>0.745</v>
       </c>
       <c r="F12">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="G12">
-        <v>43.649</v>
+        <v>26.543</v>
       </c>
       <c r="H12">
-        <v>48.134</v>
+        <v>29.464</v>
       </c>
       <c r="I12">
-        <v>43.586</v>
+        <v>26.44</v>
       </c>
       <c r="J12">
-        <v>48.05</v>
+        <v>29.48</v>
       </c>
       <c r="K12">
-        <v>43.648</v>
+        <v>26.615</v>
       </c>
       <c r="L12">
-        <v>48.112</v>
+        <v>29.655</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>48.641</v>
+        <v>28.921</v>
       </c>
       <c r="D13">
-        <v>1.253</v>
+        <v>0.504</v>
       </c>
       <c r="E13">
-        <v>1.119</v>
+        <v>0.71</v>
       </c>
       <c r="F13">
-        <v>0.035</v>
+        <v>0.022</v>
       </c>
       <c r="G13">
-        <v>46.455</v>
+        <v>27.487</v>
       </c>
       <c r="H13">
-        <v>50.843</v>
+        <v>30.271</v>
       </c>
       <c r="I13">
-        <v>46.367</v>
+        <v>27.418</v>
       </c>
       <c r="J13">
-        <v>50.799</v>
+        <v>30.272</v>
       </c>
       <c r="K13">
-        <v>46.49</v>
+        <v>27.529</v>
       </c>
       <c r="L13">
-        <v>50.923</v>
+        <v>30.383</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>43.014</v>
+        <v>24.682</v>
       </c>
       <c r="D14">
-        <v>1.054</v>
+        <v>0.365</v>
       </c>
       <c r="E14">
-        <v>1.027</v>
+        <v>0.604</v>
       </c>
       <c r="F14">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="G14">
-        <v>40.915</v>
+        <v>23.491</v>
       </c>
       <c r="H14">
-        <v>44.94</v>
+        <v>25.86</v>
       </c>
       <c r="I14">
-        <v>40.873</v>
+        <v>23.517</v>
       </c>
       <c r="J14">
-        <v>44.936</v>
+        <v>25.803</v>
       </c>
       <c r="K14">
-        <v>41.006</v>
+        <v>23.555</v>
       </c>
       <c r="L14">
-        <v>45.068</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>44.602</v>
+        <v>24.888</v>
       </c>
       <c r="D15">
-        <v>1.11</v>
+        <v>0.399</v>
       </c>
       <c r="E15">
-        <v>1.053</v>
+        <v>0.632</v>
       </c>
       <c r="F15">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="G15">
-        <v>42.505</v>
+        <v>23.657</v>
       </c>
       <c r="H15">
-        <v>46.634</v>
+        <v>26.133</v>
       </c>
       <c r="I15">
-        <v>42.457</v>
+        <v>23.668</v>
       </c>
       <c r="J15">
-        <v>46.649</v>
+        <v>26.115</v>
       </c>
       <c r="K15">
-        <v>42.524</v>
+        <v>23.669</v>
       </c>
       <c r="L15">
-        <v>46.716</v>
+        <v>26.115</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>42.736</v>
+        <v>23.195</v>
       </c>
       <c r="D16">
-        <v>1.26</v>
+        <v>0.437</v>
       </c>
       <c r="E16">
-        <v>1.122</v>
+        <v>0.661</v>
       </c>
       <c r="F16">
-        <v>0.035</v>
+        <v>0.021</v>
       </c>
       <c r="G16">
-        <v>40.534</v>
+        <v>21.84</v>
       </c>
       <c r="H16">
-        <v>44.934</v>
+        <v>24.43</v>
       </c>
       <c r="I16">
-        <v>40.46</v>
+        <v>21.805</v>
       </c>
       <c r="J16">
-        <v>44.865</v>
+        <v>24.377</v>
       </c>
       <c r="K16">
-        <v>40.605</v>
+        <v>21.953</v>
       </c>
       <c r="L16">
-        <v>45.01</v>
+        <v>24.525</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>43.742</v>
+        <v>23.018</v>
       </c>
       <c r="D17">
-        <v>1.359</v>
+        <v>0.391</v>
       </c>
       <c r="E17">
-        <v>1.166</v>
+        <v>0.625</v>
       </c>
       <c r="F17">
-        <v>0.037</v>
+        <v>0.02</v>
       </c>
       <c r="G17">
-        <v>41.417</v>
+        <v>21.747</v>
       </c>
       <c r="H17">
-        <v>45.985</v>
+        <v>24.198</v>
       </c>
       <c r="I17">
-        <v>41.515</v>
+        <v>21.732</v>
       </c>
       <c r="J17">
-        <v>46</v>
+        <v>24.23</v>
       </c>
       <c r="K17">
-        <v>41.443</v>
+        <v>21.761</v>
       </c>
       <c r="L17">
-        <v>45.928</v>
+        <v>24.259</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>44.479</v>
+        <v>22.642</v>
       </c>
       <c r="D18">
-        <v>1.473</v>
+        <v>0.415</v>
       </c>
       <c r="E18">
-        <v>1.214</v>
+        <v>0.644</v>
       </c>
       <c r="F18">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="G18">
-        <v>42.044</v>
+        <v>21.365</v>
       </c>
       <c r="H18">
-        <v>46.801</v>
+        <v>23.889</v>
       </c>
       <c r="I18">
-        <v>42.116</v>
+        <v>21.309</v>
       </c>
       <c r="J18">
-        <v>46.772</v>
+        <v>23.829</v>
       </c>
       <c r="K18">
-        <v>42.13</v>
+        <v>21.439</v>
       </c>
       <c r="L18">
-        <v>46.786</v>
+        <v>23.959</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>42.193</v>
+        <v>20.894</v>
       </c>
       <c r="D19">
-        <v>1.393</v>
+        <v>0.374</v>
       </c>
       <c r="E19">
-        <v>1.18</v>
+        <v>0.612</v>
       </c>
       <c r="F19">
-        <v>0.037</v>
+        <v>0.019</v>
       </c>
       <c r="G19">
-        <v>39.946</v>
+        <v>19.637</v>
       </c>
       <c r="H19">
-        <v>44.572</v>
+        <v>22.035</v>
       </c>
       <c r="I19">
-        <v>39.78</v>
+        <v>19.6</v>
       </c>
       <c r="J19">
-        <v>44.476</v>
+        <v>22.007</v>
       </c>
       <c r="K19">
-        <v>39.976</v>
+        <v>19.722</v>
       </c>
       <c r="L19">
-        <v>44.672</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>41.836</v>
+        <v>20.094</v>
       </c>
       <c r="D20">
-        <v>1.53</v>
+        <v>0.34</v>
       </c>
       <c r="E20">
-        <v>1.237</v>
+        <v>0.583</v>
       </c>
       <c r="F20">
-        <v>0.039</v>
+        <v>0.018</v>
       </c>
       <c r="G20">
-        <v>39.404</v>
+        <v>18.938</v>
       </c>
       <c r="H20">
-        <v>44.252</v>
+        <v>21.222</v>
       </c>
       <c r="I20">
-        <v>39.381</v>
+        <v>18.854</v>
       </c>
       <c r="J20">
-        <v>44.194</v>
+        <v>21.224</v>
       </c>
       <c r="K20">
-        <v>39.469</v>
+        <v>18.95</v>
       </c>
       <c r="L20">
-        <v>44.282</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>42.089</v>
+        <v>19.637</v>
       </c>
       <c r="D21">
-        <v>1.437</v>
+        <v>0.347</v>
       </c>
       <c r="E21">
-        <v>1.199</v>
+        <v>0.589</v>
       </c>
       <c r="F21">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="G21">
-        <v>39.654</v>
+        <v>18.408</v>
       </c>
       <c r="H21">
-        <v>44.352</v>
+        <v>20.717</v>
       </c>
       <c r="I21">
-        <v>39.503</v>
+        <v>18.345</v>
       </c>
       <c r="J21">
-        <v>44.204</v>
+        <v>20.723</v>
       </c>
       <c r="K21">
-        <v>39.889</v>
+        <v>18.477</v>
       </c>
       <c r="L21">
-        <v>44.589</v>
+        <v>20.855</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>41.932</v>
+        <v>18.891</v>
       </c>
       <c r="D22">
-        <v>1.736</v>
+        <v>0.39</v>
       </c>
       <c r="E22">
-        <v>1.318</v>
+        <v>0.625</v>
       </c>
       <c r="F22">
-        <v>0.042</v>
+        <v>0.02</v>
       </c>
       <c r="G22">
-        <v>39.312</v>
+        <v>17.68</v>
       </c>
       <c r="H22">
-        <v>44.477</v>
+        <v>20.129</v>
       </c>
       <c r="I22">
-        <v>39.159</v>
+        <v>17.669</v>
       </c>
       <c r="J22">
-        <v>44.445</v>
+        <v>20.101</v>
       </c>
       <c r="K22">
-        <v>39.381</v>
+        <v>17.694</v>
       </c>
       <c r="L22">
-        <v>44.667</v>
+        <v>20.126</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>39.753</v>
+        <v>17.35</v>
       </c>
       <c r="D23">
-        <v>1.414</v>
+        <v>0.294</v>
       </c>
       <c r="E23">
-        <v>1.189</v>
+        <v>0.542</v>
       </c>
       <c r="F23">
-        <v>0.038</v>
+        <v>0.017</v>
       </c>
       <c r="G23">
-        <v>37.44</v>
+        <v>16.322</v>
       </c>
       <c r="H23">
-        <v>42.102</v>
+        <v>18.449</v>
       </c>
       <c r="I23">
-        <v>37.365</v>
+        <v>16.288</v>
       </c>
       <c r="J23">
-        <v>42.127</v>
+        <v>18.488</v>
       </c>
       <c r="K23">
-        <v>37.398</v>
+        <v>16.247</v>
       </c>
       <c r="L23">
-        <v>42.159</v>
+        <v>18.448</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>40.776</v>
+        <v>17.204</v>
       </c>
       <c r="D24">
-        <v>1.86</v>
+        <v>0.353</v>
       </c>
       <c r="E24">
-        <v>1.364</v>
+        <v>0.594</v>
       </c>
       <c r="F24">
-        <v>0.043</v>
+        <v>0.019</v>
       </c>
       <c r="G24">
-        <v>37.993</v>
+        <v>16.042</v>
       </c>
       <c r="H24">
-        <v>43.339</v>
+        <v>18.371</v>
       </c>
       <c r="I24">
-        <v>38.007</v>
+        <v>16.031</v>
       </c>
       <c r="J24">
-        <v>43.291</v>
+        <v>18.412</v>
       </c>
       <c r="K24">
-        <v>38.151</v>
+        <v>15.998</v>
       </c>
       <c r="L24">
-        <v>43.434</v>
+        <v>18.379</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>38.273</v>
+        <v>15.641</v>
       </c>
       <c r="D25">
-        <v>1.47</v>
+        <v>0.243</v>
       </c>
       <c r="E25">
-        <v>1.213</v>
+        <v>0.492</v>
       </c>
       <c r="F25">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="G25">
-        <v>35.869</v>
+        <v>14.663</v>
       </c>
       <c r="H25">
-        <v>40.623</v>
+        <v>16.594</v>
       </c>
       <c r="I25">
-        <v>35.88</v>
+        <v>14.594</v>
       </c>
       <c r="J25">
-        <v>40.57</v>
+        <v>16.509</v>
       </c>
       <c r="K25">
-        <v>35.949</v>
+        <v>14.761</v>
       </c>
       <c r="L25">
-        <v>40.639</v>
+        <v>16.675</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>267.381</v>
+        <v>267.821</v>
       </c>
       <c r="D26">
-        <v>5.522</v>
+        <v>5.834</v>
       </c>
       <c r="E26">
-        <v>2.35</v>
+        <v>2.415</v>
       </c>
       <c r="F26">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="G26">
-        <v>262.866</v>
+        <v>263.181</v>
       </c>
       <c r="H26">
-        <v>272.077</v>
+        <v>272.649</v>
       </c>
       <c r="I26">
-        <v>262.679</v>
+        <v>263.067</v>
       </c>
       <c r="J26">
-        <v>271.864</v>
+        <v>272.392</v>
       </c>
       <c r="K26">
-        <v>262.988</v>
+        <v>263.344</v>
       </c>
       <c r="L26">
-        <v>272.174</v>
+        <v>272.669</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>177.567</v>
+        <v>177.949</v>
       </c>
       <c r="D27">
-        <v>3.133</v>
+        <v>3.48</v>
       </c>
       <c r="E27">
-        <v>1.77</v>
+        <v>1.866</v>
       </c>
       <c r="F27">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="G27">
-        <v>174.102</v>
+        <v>174.315</v>
       </c>
       <c r="H27">
-        <v>181.04</v>
+        <v>181.628</v>
       </c>
       <c r="I27">
-        <v>173.956</v>
+        <v>174.101</v>
       </c>
       <c r="J27">
-        <v>181.044</v>
+        <v>181.606</v>
       </c>
       <c r="K27">
-        <v>174.093</v>
+        <v>174.314</v>
       </c>
       <c r="L27">
-        <v>181.181</v>
+        <v>181.818</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>122.467</v>
+        <v>117.42</v>
       </c>
       <c r="D28">
-        <v>2.554</v>
+        <v>2.387</v>
       </c>
       <c r="E28">
-        <v>1.598</v>
+        <v>1.545</v>
       </c>
       <c r="F28">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="G28">
-        <v>119.351</v>
+        <v>114.43</v>
       </c>
       <c r="H28">
-        <v>125.616</v>
+        <v>120.486</v>
       </c>
       <c r="I28">
-        <v>119.153</v>
+        <v>114.281</v>
       </c>
       <c r="J28">
-        <v>125.485</v>
+        <v>120.452</v>
       </c>
       <c r="K28">
-        <v>119.465</v>
+        <v>114.425</v>
       </c>
       <c r="L28">
-        <v>125.798</v>
+        <v>120.596</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>90.712</v>
+        <v>83.565</v>
       </c>
       <c r="D29">
-        <v>3.741</v>
+        <v>3.16</v>
       </c>
       <c r="E29">
-        <v>1.934</v>
+        <v>1.778</v>
       </c>
       <c r="F29">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="G29">
-        <v>86.93300000000001</v>
+        <v>80.09399999999999</v>
       </c>
       <c r="H29">
-        <v>94.515</v>
+        <v>87.063</v>
       </c>
       <c r="I29">
-        <v>86.437</v>
+        <v>79.667</v>
       </c>
       <c r="J29">
-        <v>94.245</v>
+        <v>86.785</v>
       </c>
       <c r="K29">
-        <v>87.191</v>
+        <v>80.35899999999999</v>
       </c>
       <c r="L29">
-        <v>95</v>
+        <v>87.477</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>75.324</v>
+        <v>64.19799999999999</v>
       </c>
       <c r="D30">
-        <v>1.653</v>
+        <v>1.206</v>
       </c>
       <c r="E30">
-        <v>1.286</v>
+        <v>1.098</v>
       </c>
       <c r="F30">
-        <v>0.041</v>
+        <v>0.035</v>
       </c>
       <c r="G30">
-        <v>72.86</v>
+        <v>62.096</v>
       </c>
       <c r="H30">
-        <v>77.899</v>
+        <v>66.401</v>
       </c>
       <c r="I30">
-        <v>72.694</v>
+        <v>61.978</v>
       </c>
       <c r="J30">
-        <v>77.798</v>
+        <v>66.39100000000001</v>
       </c>
       <c r="K30">
-        <v>72.90600000000001</v>
+        <v>62.055</v>
       </c>
       <c r="L30">
-        <v>78.01000000000001</v>
+        <v>66.468</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>64.363</v>
+        <v>52.251</v>
       </c>
       <c r="D31">
-        <v>1.515</v>
+        <v>1.008</v>
       </c>
       <c r="E31">
-        <v>1.231</v>
+        <v>1.004</v>
       </c>
       <c r="F31">
-        <v>0.039</v>
+        <v>0.032</v>
       </c>
       <c r="G31">
-        <v>61.901</v>
+        <v>50.243</v>
       </c>
       <c r="H31">
-        <v>66.72499999999999</v>
+        <v>54.179</v>
       </c>
       <c r="I31">
-        <v>61.864</v>
+        <v>50.196</v>
       </c>
       <c r="J31">
-        <v>66.70399999999999</v>
+        <v>54.118</v>
       </c>
       <c r="K31">
-        <v>61.971</v>
+        <v>50.345</v>
       </c>
       <c r="L31">
-        <v>66.812</v>
+        <v>54.266</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>57.66</v>
+        <v>45.048</v>
       </c>
       <c r="D32">
-        <v>1.466</v>
+        <v>0.914</v>
       </c>
       <c r="E32">
-        <v>1.211</v>
+        <v>0.956</v>
       </c>
       <c r="F32">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="G32">
-        <v>55.308</v>
+        <v>43.19</v>
       </c>
       <c r="H32">
-        <v>60.054</v>
+        <v>46.937</v>
       </c>
       <c r="I32">
-        <v>55.281</v>
+        <v>43.173</v>
       </c>
       <c r="J32">
-        <v>60.03</v>
+        <v>46.941</v>
       </c>
       <c r="K32">
-        <v>55.311</v>
+        <v>43.17</v>
       </c>
       <c r="L32">
-        <v>60.059</v>
+        <v>46.938</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>51.72</v>
+        <v>38.963</v>
       </c>
       <c r="D33">
-        <v>1.243</v>
+        <v>0.738</v>
       </c>
       <c r="E33">
-        <v>1.115</v>
+        <v>0.859</v>
       </c>
       <c r="F33">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="G33">
-        <v>49.443</v>
+        <v>37.209</v>
       </c>
       <c r="H33">
-        <v>53.813</v>
+        <v>40.575</v>
       </c>
       <c r="I33">
-        <v>49.458</v>
+        <v>37.185</v>
       </c>
       <c r="J33">
-        <v>53.95</v>
+        <v>40.607</v>
       </c>
       <c r="K33">
-        <v>49.399</v>
+        <v>37.248</v>
       </c>
       <c r="L33">
-        <v>53.89</v>
+        <v>40.669</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>47.995</v>
+        <v>34.93</v>
       </c>
       <c r="D34">
-        <v>1.108</v>
+        <v>0.599</v>
       </c>
       <c r="E34">
-        <v>1.053</v>
+        <v>0.774</v>
       </c>
       <c r="F34">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="G34">
-        <v>45.838</v>
+        <v>33.342</v>
       </c>
       <c r="H34">
-        <v>49.963</v>
+        <v>36.376</v>
       </c>
       <c r="I34">
-        <v>45.807</v>
+        <v>33.302</v>
       </c>
       <c r="J34">
-        <v>49.917</v>
+        <v>36.382</v>
       </c>
       <c r="K34">
-        <v>45.979</v>
+        <v>33.407</v>
       </c>
       <c r="L34">
-        <v>50.088</v>
+        <v>36.487</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>47.67</v>
+        <v>33.678</v>
       </c>
       <c r="D35">
-        <v>1.131</v>
+        <v>0.581</v>
       </c>
       <c r="E35">
-        <v>1.063</v>
+        <v>0.762</v>
       </c>
       <c r="F35">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="G35">
-        <v>45.521</v>
+        <v>32.139</v>
       </c>
       <c r="H35">
-        <v>49.689</v>
+        <v>35.126</v>
       </c>
       <c r="I35">
-        <v>45.332</v>
+        <v>32.04</v>
       </c>
       <c r="J35">
-        <v>49.715</v>
+        <v>35.163</v>
       </c>
       <c r="K35">
-        <v>45.56</v>
+        <v>32.148</v>
       </c>
       <c r="L35">
-        <v>49.943</v>
+        <v>35.271</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>45.807</v>
+        <v>31.284</v>
       </c>
       <c r="D36">
-        <v>1.309</v>
+        <v>0.628</v>
       </c>
       <c r="E36">
-        <v>1.144</v>
+        <v>0.793</v>
       </c>
       <c r="F36">
-        <v>0.036</v>
+        <v>0.025</v>
       </c>
       <c r="G36">
-        <v>43.649</v>
+        <v>29.788</v>
       </c>
       <c r="H36">
-        <v>48.134</v>
+        <v>32.895</v>
       </c>
       <c r="I36">
-        <v>43.586</v>
+        <v>29.765</v>
       </c>
       <c r="J36">
-        <v>48.05</v>
+        <v>32.819</v>
       </c>
       <c r="K36">
-        <v>43.648</v>
+        <v>29.807</v>
       </c>
       <c r="L36">
-        <v>48.112</v>
+        <v>32.861</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>48.641</v>
+        <v>32.263</v>
       </c>
       <c r="D37">
-        <v>1.253</v>
+        <v>0.571</v>
       </c>
       <c r="E37">
-        <v>1.119</v>
+        <v>0.756</v>
       </c>
       <c r="F37">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="G37">
-        <v>46.455</v>
+        <v>30.785</v>
       </c>
       <c r="H37">
-        <v>50.843</v>
+        <v>33.749</v>
       </c>
       <c r="I37">
-        <v>46.367</v>
+        <v>30.738</v>
       </c>
       <c r="J37">
-        <v>50.799</v>
+        <v>33.696</v>
       </c>
       <c r="K37">
-        <v>46.49</v>
+        <v>30.834</v>
       </c>
       <c r="L37">
-        <v>50.923</v>
+        <v>33.792</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>43.014</v>
+        <v>27.58</v>
       </c>
       <c r="D38">
-        <v>1.054</v>
+        <v>0.444</v>
       </c>
       <c r="E38">
-        <v>1.027</v>
+        <v>0.666</v>
       </c>
       <c r="F38">
-        <v>0.032</v>
+        <v>0.021</v>
       </c>
       <c r="G38">
-        <v>40.915</v>
+        <v>26.218</v>
       </c>
       <c r="H38">
-        <v>44.94</v>
+        <v>28.829</v>
       </c>
       <c r="I38">
-        <v>40.873</v>
+        <v>26.153</v>
       </c>
       <c r="J38">
-        <v>44.936</v>
+        <v>28.831</v>
       </c>
       <c r="K38">
-        <v>41.006</v>
+        <v>26.273</v>
       </c>
       <c r="L38">
-        <v>45.068</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>44.602</v>
+        <v>27.799</v>
       </c>
       <c r="D39">
-        <v>1.11</v>
+        <v>0.444</v>
       </c>
       <c r="E39">
-        <v>1.053</v>
+        <v>0.666</v>
       </c>
       <c r="F39">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="G39">
-        <v>42.505</v>
+        <v>26.474</v>
       </c>
       <c r="H39">
-        <v>46.634</v>
+        <v>29.085</v>
       </c>
       <c r="I39">
-        <v>42.457</v>
+        <v>26.424</v>
       </c>
       <c r="J39">
-        <v>46.649</v>
+        <v>29.113</v>
       </c>
       <c r="K39">
-        <v>42.524</v>
+        <v>26.466</v>
       </c>
       <c r="L39">
-        <v>46.716</v>
+        <v>29.155</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>42.736</v>
+        <v>25.861</v>
       </c>
       <c r="D40">
-        <v>1.26</v>
+        <v>0.482</v>
       </c>
       <c r="E40">
-        <v>1.122</v>
+        <v>0.694</v>
       </c>
       <c r="F40">
-        <v>0.035</v>
+        <v>0.022</v>
       </c>
       <c r="G40">
-        <v>40.534</v>
+        <v>24.502</v>
       </c>
       <c r="H40">
-        <v>44.934</v>
+        <v>27.223</v>
       </c>
       <c r="I40">
-        <v>40.46</v>
+        <v>24.43</v>
       </c>
       <c r="J40">
-        <v>44.865</v>
+        <v>27.149</v>
       </c>
       <c r="K40">
-        <v>40.605</v>
+        <v>24.574</v>
       </c>
       <c r="L40">
-        <v>45.01</v>
+        <v>27.294</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>43.742</v>
+        <v>25.682</v>
       </c>
       <c r="D41">
-        <v>1.359</v>
+        <v>0.49</v>
       </c>
       <c r="E41">
-        <v>1.166</v>
+        <v>0.7</v>
       </c>
       <c r="F41">
-        <v>0.037</v>
+        <v>0.022</v>
       </c>
       <c r="G41">
-        <v>41.417</v>
+        <v>24.291</v>
       </c>
       <c r="H41">
-        <v>45.985</v>
+        <v>27.034</v>
       </c>
       <c r="I41">
-        <v>41.515</v>
+        <v>24.277</v>
       </c>
       <c r="J41">
-        <v>46</v>
+        <v>27.016</v>
       </c>
       <c r="K41">
-        <v>41.443</v>
+        <v>24.329</v>
       </c>
       <c r="L41">
-        <v>45.928</v>
+        <v>27.068</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>44.479</v>
+        <v>25.284</v>
       </c>
       <c r="D42">
-        <v>1.473</v>
+        <v>0.501</v>
       </c>
       <c r="E42">
-        <v>1.214</v>
+        <v>0.708</v>
       </c>
       <c r="F42">
-        <v>0.038</v>
+        <v>0.022</v>
       </c>
       <c r="G42">
-        <v>42.044</v>
+        <v>23.867</v>
       </c>
       <c r="H42">
-        <v>46.801</v>
+        <v>26.641</v>
       </c>
       <c r="I42">
-        <v>42.116</v>
+        <v>23.83</v>
       </c>
       <c r="J42">
-        <v>46.772</v>
+        <v>26.638</v>
       </c>
       <c r="K42">
-        <v>42.13</v>
+        <v>23.9</v>
       </c>
       <c r="L42">
-        <v>46.786</v>
+        <v>26.709</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>42.193</v>
+        <v>23.273</v>
       </c>
       <c r="D43">
-        <v>1.393</v>
+        <v>0.443</v>
       </c>
       <c r="E43">
-        <v>1.18</v>
+        <v>0.666</v>
       </c>
       <c r="F43">
-        <v>0.037</v>
+        <v>0.021</v>
       </c>
       <c r="G43">
-        <v>39.946</v>
+        <v>22.01</v>
       </c>
       <c r="H43">
-        <v>44.572</v>
+        <v>24.619</v>
       </c>
       <c r="I43">
-        <v>39.78</v>
+        <v>21.943</v>
       </c>
       <c r="J43">
-        <v>44.476</v>
+        <v>24.548</v>
       </c>
       <c r="K43">
-        <v>39.976</v>
+        <v>22.04</v>
       </c>
       <c r="L43">
-        <v>44.672</v>
+        <v>24.644</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>41.836</v>
+        <v>22.424</v>
       </c>
       <c r="D44">
-        <v>1.53</v>
+        <v>0.459</v>
       </c>
       <c r="E44">
-        <v>1.237</v>
+        <v>0.677</v>
       </c>
       <c r="F44">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="G44">
-        <v>39.404</v>
+        <v>21.099</v>
       </c>
       <c r="H44">
-        <v>44.252</v>
+        <v>23.754</v>
       </c>
       <c r="I44">
-        <v>39.381</v>
+        <v>21.064</v>
       </c>
       <c r="J44">
-        <v>44.194</v>
+        <v>23.699</v>
       </c>
       <c r="K44">
-        <v>39.469</v>
+        <v>21.152</v>
       </c>
       <c r="L44">
-        <v>44.282</v>
+        <v>23.787</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>42.089</v>
+        <v>21.902</v>
       </c>
       <c r="D45">
-        <v>1.437</v>
+        <v>0.409</v>
       </c>
       <c r="E45">
-        <v>1.199</v>
+        <v>0.639</v>
       </c>
       <c r="F45">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="G45">
-        <v>39.654</v>
+        <v>20.609</v>
       </c>
       <c r="H45">
-        <v>44.352</v>
+        <v>23.114</v>
       </c>
       <c r="I45">
-        <v>39.503</v>
+        <v>20.507</v>
       </c>
       <c r="J45">
-        <v>44.204</v>
+        <v>23.111</v>
       </c>
       <c r="K45">
-        <v>39.889</v>
+        <v>20.652</v>
       </c>
       <c r="L45">
-        <v>44.589</v>
+        <v>23.257</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>41.932</v>
+        <v>21.103</v>
       </c>
       <c r="D46">
-        <v>1.736</v>
+        <v>0.448</v>
       </c>
       <c r="E46">
-        <v>1.318</v>
+        <v>0.669</v>
       </c>
       <c r="F46">
-        <v>0.042</v>
+        <v>0.021</v>
       </c>
       <c r="G46">
-        <v>39.312</v>
+        <v>19.78</v>
       </c>
       <c r="H46">
-        <v>44.477</v>
+        <v>22.403</v>
       </c>
       <c r="I46">
-        <v>39.159</v>
+        <v>19.713</v>
       </c>
       <c r="J46">
-        <v>44.445</v>
+        <v>22.374</v>
       </c>
       <c r="K46">
-        <v>39.381</v>
+        <v>19.821</v>
       </c>
       <c r="L46">
-        <v>44.667</v>
+        <v>22.482</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>39.753</v>
+        <v>19.384</v>
       </c>
       <c r="D47">
-        <v>1.414</v>
+        <v>0.354</v>
       </c>
       <c r="E47">
-        <v>1.189</v>
+        <v>0.595</v>
       </c>
       <c r="F47">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="G47">
-        <v>37.44</v>
+        <v>18.229</v>
       </c>
       <c r="H47">
-        <v>42.102</v>
+        <v>20.562</v>
       </c>
       <c r="I47">
-        <v>37.365</v>
+        <v>18.206</v>
       </c>
       <c r="J47">
-        <v>42.127</v>
+        <v>20.536</v>
       </c>
       <c r="K47">
-        <v>37.398</v>
+        <v>18.244</v>
       </c>
       <c r="L47">
-        <v>42.159</v>
+        <v>20.574</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>40.776</v>
+        <v>19.233</v>
       </c>
       <c r="D48">
-        <v>1.86</v>
+        <v>0.422</v>
       </c>
       <c r="E48">
-        <v>1.364</v>
+        <v>0.65</v>
       </c>
       <c r="F48">
-        <v>0.043</v>
+        <v>0.021</v>
       </c>
       <c r="G48">
-        <v>37.993</v>
+        <v>17.91</v>
       </c>
       <c r="H48">
-        <v>43.339</v>
+        <v>20.456</v>
       </c>
       <c r="I48">
-        <v>38.007</v>
+        <v>17.946</v>
       </c>
       <c r="J48">
-        <v>43.291</v>
+        <v>20.484</v>
       </c>
       <c r="K48">
-        <v>38.151</v>
+        <v>17.932</v>
       </c>
       <c r="L48">
-        <v>43.434</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>38.273</v>
+        <v>17.46</v>
       </c>
       <c r="D49">
-        <v>1.47</v>
+        <v>0.315</v>
       </c>
       <c r="E49">
-        <v>1.213</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F49">
-        <v>0.038</v>
+        <v>0.018</v>
       </c>
       <c r="G49">
-        <v>35.869</v>
+        <v>16.349</v>
       </c>
       <c r="H49">
-        <v>40.623</v>
+        <v>18.55</v>
       </c>
       <c r="I49">
-        <v>35.88</v>
+        <v>16.436</v>
       </c>
       <c r="J49">
-        <v>40.57</v>
+        <v>18.532</v>
       </c>
       <c r="K49">
-        <v>35.949</v>
+        <v>16.378</v>
       </c>
       <c r="L49">
-        <v>40.639</v>
+        <v>18.474</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>239.905</v>
+        <v>243.364</v>
       </c>
       <c r="D2">
-        <v>4.832</v>
+        <v>5.128</v>
       </c>
       <c r="E2">
-        <v>2.198</v>
+        <v>2.265</v>
       </c>
       <c r="F2">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G2">
-        <v>235.656</v>
+        <v>238.996</v>
       </c>
       <c r="H2">
-        <v>244.273</v>
+        <v>247.873</v>
       </c>
       <c r="I2">
-        <v>235.629</v>
+        <v>239.039</v>
       </c>
       <c r="J2">
-        <v>243.948</v>
+        <v>247.649</v>
       </c>
       <c r="K2">
-        <v>235.922</v>
+        <v>239.15</v>
       </c>
       <c r="L2">
-        <v>244.241</v>
+        <v>247.76</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>159.44</v>
+        <v>163.797</v>
       </c>
       <c r="D3">
-        <v>2.608</v>
+        <v>2.955</v>
       </c>
       <c r="E3">
-        <v>1.615</v>
+        <v>1.719</v>
       </c>
       <c r="F3">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="G3">
-        <v>156.2</v>
+        <v>160.356</v>
       </c>
       <c r="H3">
-        <v>162.53</v>
+        <v>167.095</v>
       </c>
       <c r="I3">
-        <v>156.071</v>
+        <v>160.2</v>
       </c>
       <c r="J3">
-        <v>162.445</v>
+        <v>167.039</v>
       </c>
       <c r="K3">
-        <v>156.359</v>
+        <v>160.484</v>
       </c>
       <c r="L3">
-        <v>162.734</v>
+        <v>167.323</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>105.234</v>
+        <v>108.975</v>
       </c>
       <c r="D4">
-        <v>2.016</v>
+        <v>2.156</v>
       </c>
       <c r="E4">
-        <v>1.42</v>
+        <v>1.468</v>
       </c>
       <c r="F4">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="G4">
-        <v>102.367</v>
+        <v>106.003</v>
       </c>
       <c r="H4">
-        <v>107.933</v>
+        <v>111.759</v>
       </c>
       <c r="I4">
-        <v>102.418</v>
+        <v>106.038</v>
       </c>
       <c r="J4">
-        <v>107.952</v>
+        <v>111.729</v>
       </c>
       <c r="K4">
-        <v>102.433</v>
+        <v>106.127</v>
       </c>
       <c r="L4">
-        <v>107.966</v>
+        <v>111.819</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>74.93300000000001</v>
+        <v>77.69199999999999</v>
       </c>
       <c r="D5">
-        <v>2.466</v>
+        <v>2.524</v>
       </c>
       <c r="E5">
-        <v>1.57</v>
+        <v>1.589</v>
       </c>
       <c r="F5">
         <v>0.05</v>
       </c>
       <c r="G5">
-        <v>71.703</v>
+        <v>74.429</v>
       </c>
       <c r="H5">
-        <v>77.85899999999999</v>
+        <v>80.65600000000001</v>
       </c>
       <c r="I5">
-        <v>71.495</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="J5">
-        <v>77.654</v>
+        <v>80.443</v>
       </c>
       <c r="K5">
-        <v>72.06100000000001</v>
+        <v>74.791</v>
       </c>
       <c r="L5">
-        <v>78.21899999999999</v>
+        <v>81.02500000000001</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>57.501</v>
+        <v>59.668</v>
       </c>
       <c r="D6">
-        <v>0.931</v>
+        <v>0.994</v>
       </c>
       <c r="E6">
-        <v>0.965</v>
+        <v>0.997</v>
       </c>
       <c r="F6">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="G6">
-        <v>55.659</v>
+        <v>57.764</v>
       </c>
       <c r="H6">
-        <v>59.442</v>
+        <v>61.672</v>
       </c>
       <c r="I6">
-        <v>55.659</v>
+        <v>57.748</v>
       </c>
       <c r="J6">
-        <v>59.439</v>
+        <v>61.699</v>
       </c>
       <c r="K6">
-        <v>55.613</v>
+        <v>57.688</v>
       </c>
       <c r="L6">
-        <v>59.393</v>
+        <v>61.639</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
+        <v>48.589</v>
+      </c>
+      <c r="D7">
+        <v>0.891</v>
+      </c>
+      <c r="E7">
+        <v>0.944</v>
+      </c>
+      <c r="F7">
+        <v>0.03</v>
+      </c>
+      <c r="G7">
+        <v>46.761</v>
+      </c>
+      <c r="H7">
+        <v>50.461</v>
+      </c>
+      <c r="I7">
         <v>46.776</v>
       </c>
-      <c r="D7">
-        <v>0.819</v>
-      </c>
-      <c r="E7">
-        <v>0.905</v>
-      </c>
-      <c r="F7">
-        <v>0.029</v>
-      </c>
-      <c r="G7">
-        <v>45.02</v>
-      </c>
-      <c r="H7">
-        <v>48.568</v>
-      </c>
-      <c r="I7">
-        <v>45.037</v>
-      </c>
       <c r="J7">
-        <v>48.489</v>
+        <v>50.388</v>
       </c>
       <c r="K7">
-        <v>45.08</v>
+        <v>46.813</v>
       </c>
       <c r="L7">
-        <v>48.533</v>
+        <v>50.425</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>40.338</v>
+        <v>41.819</v>
       </c>
       <c r="D8">
-        <v>0.71</v>
+        <v>0.773</v>
       </c>
       <c r="E8">
-        <v>0.843</v>
+        <v>0.879</v>
       </c>
       <c r="F8">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="G8">
-        <v>38.724</v>
+        <v>40.136</v>
       </c>
       <c r="H8">
-        <v>42.028</v>
+        <v>43.583</v>
       </c>
       <c r="I8">
-        <v>38.643</v>
+        <v>40.061</v>
       </c>
       <c r="J8">
-        <v>42.007</v>
+        <v>43.538</v>
       </c>
       <c r="K8">
-        <v>38.707</v>
+        <v>40.141</v>
       </c>
       <c r="L8">
-        <v>42.071</v>
+        <v>43.618</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>34.879</v>
+        <v>36.247</v>
       </c>
       <c r="D9">
-        <v>0.621</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="E9">
-        <v>0.788</v>
+        <v>0.831</v>
       </c>
       <c r="F9">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="G9">
-        <v>33.312</v>
+        <v>34.599</v>
       </c>
       <c r="H9">
-        <v>36.401</v>
+        <v>37.857</v>
       </c>
       <c r="I9">
-        <v>33.244</v>
+        <v>34.566</v>
       </c>
       <c r="J9">
-        <v>36.395</v>
+        <v>37.859</v>
       </c>
       <c r="K9">
-        <v>33.341</v>
+        <v>34.616</v>
       </c>
       <c r="L9">
-        <v>36.491</v>
+        <v>37.909</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>31.263</v>
+        <v>32.371</v>
       </c>
       <c r="D10">
-        <v>0.538</v>
+        <v>0.586</v>
       </c>
       <c r="E10">
-        <v>0.734</v>
+        <v>0.765</v>
       </c>
       <c r="F10">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G10">
-        <v>29.811</v>
+        <v>30.859</v>
       </c>
       <c r="H10">
-        <v>32.687</v>
+        <v>33.859</v>
       </c>
       <c r="I10">
-        <v>29.799</v>
+        <v>30.83</v>
       </c>
       <c r="J10">
-        <v>32.689</v>
+        <v>33.851</v>
       </c>
       <c r="K10">
-        <v>29.822</v>
+        <v>30.879</v>
       </c>
       <c r="L10">
-        <v>32.712</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>30.158</v>
+        <v>31.212</v>
       </c>
       <c r="D11">
-        <v>0.492</v>
+        <v>0.528</v>
       </c>
       <c r="E11">
-        <v>0.701</v>
+        <v>0.726</v>
       </c>
       <c r="F11">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G11">
-        <v>28.76</v>
+        <v>29.761</v>
       </c>
       <c r="H11">
-        <v>31.508</v>
+        <v>32.609</v>
       </c>
       <c r="I11">
-        <v>28.732</v>
+        <v>29.751</v>
       </c>
       <c r="J11">
-        <v>31.471</v>
+        <v>32.566</v>
       </c>
       <c r="K11">
-        <v>28.821</v>
+        <v>29.831</v>
       </c>
       <c r="L11">
-        <v>31.56</v>
+        <v>32.646</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>28.092</v>
+        <v>29.098</v>
       </c>
       <c r="D12">
-        <v>0.555</v>
+        <v>0.592</v>
       </c>
       <c r="E12">
-        <v>0.745</v>
+        <v>0.769</v>
       </c>
       <c r="F12">
         <v>0.024</v>
       </c>
       <c r="G12">
-        <v>26.543</v>
+        <v>27.502</v>
       </c>
       <c r="H12">
-        <v>29.464</v>
+        <v>30.517</v>
       </c>
       <c r="I12">
-        <v>26.44</v>
+        <v>27.386</v>
       </c>
       <c r="J12">
-        <v>29.48</v>
+        <v>30.516</v>
       </c>
       <c r="K12">
-        <v>26.615</v>
+        <v>27.591</v>
       </c>
       <c r="L12">
-        <v>29.655</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>28.921</v>
+        <v>29.876</v>
       </c>
       <c r="D13">
-        <v>0.504</v>
+        <v>0.53</v>
       </c>
       <c r="E13">
-        <v>0.71</v>
+        <v>0.728</v>
       </c>
       <c r="F13">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G13">
-        <v>27.487</v>
+        <v>28.406</v>
       </c>
       <c r="H13">
-        <v>30.271</v>
+        <v>31.259</v>
       </c>
       <c r="I13">
-        <v>27.418</v>
+        <v>28.345</v>
       </c>
       <c r="J13">
-        <v>30.272</v>
+        <v>31.24</v>
       </c>
       <c r="K13">
-        <v>27.529</v>
+        <v>28.469</v>
       </c>
       <c r="L13">
-        <v>30.383</v>
+        <v>31.364</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>24.682</v>
+        <v>25.568</v>
       </c>
       <c r="D14">
-        <v>0.365</v>
+        <v>0.396</v>
       </c>
       <c r="E14">
-        <v>0.604</v>
+        <v>0.629</v>
       </c>
       <c r="F14">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G14">
-        <v>23.491</v>
+        <v>24.327</v>
       </c>
       <c r="H14">
-        <v>25.86</v>
+        <v>26.793</v>
       </c>
       <c r="I14">
-        <v>23.517</v>
+        <v>24.35</v>
       </c>
       <c r="J14">
-        <v>25.803</v>
+        <v>26.707</v>
       </c>
       <c r="K14">
-        <v>23.555</v>
+        <v>24.421</v>
       </c>
       <c r="L14">
-        <v>25.84</v>
+        <v>26.778</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>24.888</v>
+        <v>25.703</v>
       </c>
       <c r="D15">
-        <v>0.399</v>
+        <v>0.421</v>
       </c>
       <c r="E15">
-        <v>0.632</v>
+        <v>0.649</v>
       </c>
       <c r="F15">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G15">
-        <v>23.657</v>
+        <v>24.44</v>
       </c>
       <c r="H15">
-        <v>26.133</v>
+        <v>26.984</v>
       </c>
       <c r="I15">
-        <v>23.668</v>
+        <v>24.47</v>
       </c>
       <c r="J15">
-        <v>26.115</v>
+        <v>26.958</v>
       </c>
       <c r="K15">
-        <v>23.669</v>
+        <v>24.457</v>
       </c>
       <c r="L15">
-        <v>26.115</v>
+        <v>26.945</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>23.195</v>
+        <v>24.038</v>
       </c>
       <c r="D16">
-        <v>0.437</v>
+        <v>0.47</v>
       </c>
       <c r="E16">
-        <v>0.661</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F16">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G16">
-        <v>21.84</v>
+        <v>22.635</v>
       </c>
       <c r="H16">
-        <v>24.43</v>
+        <v>25.322</v>
       </c>
       <c r="I16">
-        <v>21.805</v>
+        <v>22.578</v>
       </c>
       <c r="J16">
-        <v>24.377</v>
+        <v>25.309</v>
       </c>
       <c r="K16">
-        <v>21.953</v>
+        <v>22.707</v>
       </c>
       <c r="L16">
-        <v>24.525</v>
+        <v>25.438</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>23.018</v>
+        <v>23.798</v>
       </c>
       <c r="D17">
-        <v>0.391</v>
+        <v>0.414</v>
       </c>
       <c r="E17">
-        <v>0.625</v>
+        <v>0.644</v>
       </c>
       <c r="F17">
         <v>0.02</v>
       </c>
       <c r="G17">
-        <v>21.747</v>
+        <v>22.488</v>
       </c>
       <c r="H17">
-        <v>24.198</v>
+        <v>25.01</v>
       </c>
       <c r="I17">
-        <v>21.732</v>
+        <v>22.49</v>
       </c>
       <c r="J17">
-        <v>24.23</v>
+        <v>25.008</v>
       </c>
       <c r="K17">
-        <v>21.761</v>
+        <v>22.539</v>
       </c>
       <c r="L17">
-        <v>24.259</v>
+        <v>25.057</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>22.642</v>
+        <v>23.407</v>
       </c>
       <c r="D18">
-        <v>0.415</v>
+        <v>0.438</v>
       </c>
       <c r="E18">
-        <v>0.644</v>
+        <v>0.662</v>
       </c>
       <c r="F18">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G18">
-        <v>21.365</v>
+        <v>22.097</v>
       </c>
       <c r="H18">
-        <v>23.889</v>
+        <v>24.691</v>
       </c>
       <c r="I18">
-        <v>21.309</v>
+        <v>22.069</v>
       </c>
       <c r="J18">
-        <v>23.829</v>
+        <v>24.614</v>
       </c>
       <c r="K18">
-        <v>21.439</v>
+        <v>22.187</v>
       </c>
       <c r="L18">
-        <v>23.959</v>
+        <v>24.732</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>20.894</v>
+        <v>21.604</v>
       </c>
       <c r="D19">
-        <v>0.374</v>
+        <v>0.392</v>
       </c>
       <c r="E19">
-        <v>0.612</v>
+        <v>0.626</v>
       </c>
       <c r="F19">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G19">
-        <v>19.637</v>
+        <v>20.324</v>
       </c>
       <c r="H19">
-        <v>22.035</v>
+        <v>22.777</v>
       </c>
       <c r="I19">
-        <v>19.6</v>
+        <v>20.275</v>
       </c>
       <c r="J19">
-        <v>22.007</v>
+        <v>22.75</v>
       </c>
       <c r="K19">
-        <v>19.722</v>
+        <v>20.405</v>
       </c>
       <c r="L19">
-        <v>22.13</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>20.094</v>
+        <v>20.816</v>
       </c>
       <c r="D20">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="E20">
-        <v>0.583</v>
+        <v>0.6</v>
       </c>
       <c r="F20">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="G20">
-        <v>18.938</v>
+        <v>19.626</v>
       </c>
       <c r="H20">
-        <v>21.222</v>
+        <v>21.976</v>
       </c>
       <c r="I20">
-        <v>18.854</v>
+        <v>19.523</v>
       </c>
       <c r="J20">
-        <v>21.224</v>
+        <v>21.961</v>
       </c>
       <c r="K20">
-        <v>18.95</v>
+        <v>19.657</v>
       </c>
       <c r="L20">
-        <v>21.32</v>
+        <v>22.095</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>19.637</v>
+        <v>20.293</v>
       </c>
       <c r="D21">
-        <v>0.347</v>
+        <v>0.371</v>
       </c>
       <c r="E21">
-        <v>0.589</v>
+        <v>0.609</v>
       </c>
       <c r="F21">
         <v>0.019</v>
       </c>
       <c r="G21">
-        <v>18.408</v>
+        <v>19.026</v>
       </c>
       <c r="H21">
-        <v>20.717</v>
+        <v>21.412</v>
       </c>
       <c r="I21">
-        <v>18.345</v>
+        <v>18.969</v>
       </c>
       <c r="J21">
-        <v>20.723</v>
+        <v>21.427</v>
       </c>
       <c r="K21">
-        <v>18.477</v>
+        <v>19.085</v>
       </c>
       <c r="L21">
-        <v>20.855</v>
+        <v>21.543</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>18.891</v>
+        <v>19.546</v>
       </c>
       <c r="D22">
-        <v>0.39</v>
+        <v>0.411</v>
       </c>
       <c r="E22">
-        <v>0.625</v>
+        <v>0.641</v>
       </c>
       <c r="F22">
         <v>0.02</v>
       </c>
       <c r="G22">
-        <v>17.68</v>
+        <v>18.305</v>
       </c>
       <c r="H22">
-        <v>20.129</v>
+        <v>20.818</v>
       </c>
       <c r="I22">
-        <v>17.669</v>
+        <v>18.305</v>
       </c>
       <c r="J22">
-        <v>20.101</v>
+        <v>20.785</v>
       </c>
       <c r="K22">
-        <v>17.694</v>
+        <v>18.322</v>
       </c>
       <c r="L22">
-        <v>20.126</v>
+        <v>20.803</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>17.35</v>
+        <v>17.941</v>
       </c>
       <c r="D23">
-        <v>0.294</v>
+        <v>0.309</v>
       </c>
       <c r="E23">
-        <v>0.542</v>
+        <v>0.556</v>
       </c>
       <c r="F23">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="G23">
-        <v>16.322</v>
+        <v>16.888</v>
       </c>
       <c r="H23">
-        <v>18.449</v>
+        <v>19.067</v>
       </c>
       <c r="I23">
-        <v>16.288</v>
+        <v>16.843</v>
       </c>
       <c r="J23">
-        <v>18.488</v>
+        <v>19.11</v>
       </c>
       <c r="K23">
-        <v>16.247</v>
+        <v>16.808</v>
       </c>
       <c r="L23">
-        <v>18.448</v>
+        <v>19.075</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>17.204</v>
+        <v>17.784</v>
       </c>
       <c r="D24">
-        <v>0.353</v>
+        <v>0.367</v>
       </c>
       <c r="E24">
-        <v>0.594</v>
+        <v>0.606</v>
       </c>
       <c r="F24">
         <v>0.019</v>
       </c>
       <c r="G24">
-        <v>16.042</v>
+        <v>16.599</v>
       </c>
       <c r="H24">
-        <v>18.371</v>
+        <v>18.972</v>
       </c>
       <c r="I24">
-        <v>16.031</v>
+        <v>16.584</v>
       </c>
       <c r="J24">
-        <v>18.412</v>
+        <v>19.012</v>
       </c>
       <c r="K24">
-        <v>15.998</v>
+        <v>16.557</v>
       </c>
       <c r="L24">
-        <v>18.379</v>
+        <v>18.986</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>15.641</v>
+        <v>16.199</v>
       </c>
       <c r="D25">
-        <v>0.243</v>
+        <v>0.256</v>
       </c>
       <c r="E25">
-        <v>0.492</v>
+        <v>0.506</v>
       </c>
       <c r="F25">
         <v>0.016</v>
       </c>
       <c r="G25">
-        <v>14.663</v>
+        <v>15.193</v>
       </c>
       <c r="H25">
-        <v>16.594</v>
+        <v>17.177</v>
       </c>
       <c r="I25">
-        <v>14.594</v>
+        <v>15.133</v>
       </c>
       <c r="J25">
-        <v>16.509</v>
+        <v>17.098</v>
       </c>
       <c r="K25">
-        <v>14.761</v>
+        <v>15.286</v>
       </c>
       <c r="L25">
-        <v>16.675</v>
+        <v>17.251</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>267.821</v>
+        <v>271.688</v>
       </c>
       <c r="D26">
-        <v>5.834</v>
+        <v>6.249</v>
       </c>
       <c r="E26">
-        <v>2.415</v>
+        <v>2.5</v>
       </c>
       <c r="F26">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="G26">
-        <v>263.181</v>
+        <v>266.884</v>
       </c>
       <c r="H26">
-        <v>272.649</v>
+        <v>276.683</v>
       </c>
       <c r="I26">
-        <v>263.067</v>
+        <v>266.827</v>
       </c>
       <c r="J26">
-        <v>272.392</v>
+        <v>276.449</v>
       </c>
       <c r="K26">
-        <v>263.344</v>
+        <v>267.022</v>
       </c>
       <c r="L26">
-        <v>272.669</v>
+        <v>276.644</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>177.949</v>
+        <v>182.813</v>
       </c>
       <c r="D27">
-        <v>3.48</v>
+        <v>3.953</v>
       </c>
       <c r="E27">
-        <v>1.866</v>
+        <v>1.988</v>
       </c>
       <c r="F27">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="G27">
-        <v>174.315</v>
+        <v>178.942</v>
       </c>
       <c r="H27">
-        <v>181.628</v>
+        <v>186.737</v>
       </c>
       <c r="I27">
-        <v>174.101</v>
+        <v>178.639</v>
       </c>
       <c r="J27">
-        <v>181.606</v>
+        <v>186.64</v>
       </c>
       <c r="K27">
-        <v>174.314</v>
+        <v>179.013</v>
       </c>
       <c r="L27">
-        <v>181.818</v>
+        <v>187.013</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>117.42</v>
+        <v>121.591</v>
       </c>
       <c r="D28">
-        <v>2.387</v>
+        <v>2.545</v>
       </c>
       <c r="E28">
-        <v>1.545</v>
+        <v>1.595</v>
       </c>
       <c r="F28">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="G28">
-        <v>114.43</v>
+        <v>118.501</v>
       </c>
       <c r="H28">
-        <v>120.486</v>
+        <v>124.756</v>
       </c>
       <c r="I28">
-        <v>114.281</v>
+        <v>118.337</v>
       </c>
       <c r="J28">
-        <v>120.452</v>
+        <v>124.657</v>
       </c>
       <c r="K28">
-        <v>114.425</v>
+        <v>118.562</v>
       </c>
       <c r="L28">
-        <v>120.596</v>
+        <v>124.882</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>83.565</v>
+        <v>86.646</v>
       </c>
       <c r="D29">
-        <v>3.16</v>
+        <v>3.227</v>
       </c>
       <c r="E29">
-        <v>1.778</v>
+        <v>1.796</v>
       </c>
       <c r="F29">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="G29">
-        <v>80.09399999999999</v>
+        <v>83.14100000000001</v>
       </c>
       <c r="H29">
-        <v>87.063</v>
+        <v>90.182</v>
       </c>
       <c r="I29">
-        <v>79.667</v>
+        <v>82.693</v>
       </c>
       <c r="J29">
-        <v>86.785</v>
+        <v>89.92400000000001</v>
       </c>
       <c r="K29">
-        <v>80.35899999999999</v>
+        <v>83.383</v>
       </c>
       <c r="L29">
-        <v>87.477</v>
+        <v>90.614</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>64.19799999999999</v>
+        <v>66.613</v>
       </c>
       <c r="D30">
-        <v>1.206</v>
+        <v>1.296</v>
       </c>
       <c r="E30">
-        <v>1.098</v>
+        <v>1.138</v>
       </c>
       <c r="F30">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="G30">
-        <v>62.096</v>
+        <v>64.44199999999999</v>
       </c>
       <c r="H30">
-        <v>66.401</v>
+        <v>68.904</v>
       </c>
       <c r="I30">
-        <v>61.978</v>
+        <v>64.3</v>
       </c>
       <c r="J30">
-        <v>66.39100000000001</v>
+        <v>68.89100000000001</v>
       </c>
       <c r="K30">
-        <v>62.055</v>
+        <v>64.39400000000001</v>
       </c>
       <c r="L30">
-        <v>66.468</v>
+        <v>68.985</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>52.251</v>
+        <v>54.278</v>
       </c>
       <c r="D31">
-        <v>1.008</v>
+        <v>1.103</v>
       </c>
       <c r="E31">
-        <v>1.004</v>
+        <v>1.05</v>
       </c>
       <c r="F31">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="G31">
-        <v>50.243</v>
+        <v>52.181</v>
       </c>
       <c r="H31">
-        <v>54.179</v>
+        <v>56.298</v>
       </c>
       <c r="I31">
-        <v>50.196</v>
+        <v>52.134</v>
       </c>
       <c r="J31">
-        <v>54.118</v>
+        <v>56.243</v>
       </c>
       <c r="K31">
-        <v>50.345</v>
+        <v>52.274</v>
       </c>
       <c r="L31">
-        <v>54.266</v>
+        <v>56.383</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>45.048</v>
+        <v>46.702</v>
       </c>
       <c r="D32">
-        <v>0.914</v>
+        <v>0.997</v>
       </c>
       <c r="E32">
-        <v>0.956</v>
+        <v>0.999</v>
       </c>
       <c r="F32">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="G32">
-        <v>43.19</v>
+        <v>44.762</v>
       </c>
       <c r="H32">
-        <v>46.937</v>
+        <v>48.676</v>
       </c>
       <c r="I32">
-        <v>43.173</v>
+        <v>44.758</v>
       </c>
       <c r="J32">
-        <v>46.941</v>
+        <v>48.691</v>
       </c>
       <c r="K32">
-        <v>43.17</v>
+        <v>44.73</v>
       </c>
       <c r="L32">
-        <v>46.938</v>
+        <v>48.663</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>38.963</v>
+        <v>40.493</v>
       </c>
       <c r="D33">
-        <v>0.738</v>
+        <v>0.824</v>
       </c>
       <c r="E33">
-        <v>0.859</v>
+        <v>0.908</v>
       </c>
       <c r="F33">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="G33">
-        <v>37.209</v>
+        <v>38.641</v>
       </c>
       <c r="H33">
-        <v>40.575</v>
+        <v>42.199</v>
       </c>
       <c r="I33">
-        <v>37.185</v>
+        <v>38.646</v>
       </c>
       <c r="J33">
-        <v>40.607</v>
+        <v>42.202</v>
       </c>
       <c r="K33">
-        <v>37.248</v>
+        <v>38.71</v>
       </c>
       <c r="L33">
-        <v>40.669</v>
+        <v>42.267</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>34.93</v>
+        <v>36.168</v>
       </c>
       <c r="D34">
-        <v>0.599</v>
+        <v>0.65</v>
       </c>
       <c r="E34">
-        <v>0.774</v>
+        <v>0.806</v>
       </c>
       <c r="F34">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G34">
-        <v>33.342</v>
+        <v>34.518</v>
       </c>
       <c r="H34">
-        <v>36.376</v>
+        <v>37.678</v>
       </c>
       <c r="I34">
-        <v>33.302</v>
+        <v>34.458</v>
       </c>
       <c r="J34">
-        <v>36.382</v>
+        <v>37.656</v>
       </c>
       <c r="K34">
-        <v>33.407</v>
+        <v>34.609</v>
       </c>
       <c r="L34">
-        <v>36.487</v>
+        <v>37.808</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>33.678</v>
+        <v>34.853</v>
       </c>
       <c r="D35">
-        <v>0.581</v>
+        <v>0.631</v>
       </c>
       <c r="E35">
-        <v>0.762</v>
+        <v>0.794</v>
       </c>
       <c r="F35">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G35">
-        <v>32.139</v>
+        <v>33.252</v>
       </c>
       <c r="H35">
-        <v>35.126</v>
+        <v>36.365</v>
       </c>
       <c r="I35">
-        <v>32.04</v>
+        <v>33.184</v>
       </c>
       <c r="J35">
-        <v>35.163</v>
+        <v>36.451</v>
       </c>
       <c r="K35">
-        <v>32.148</v>
+        <v>33.211</v>
       </c>
       <c r="L35">
-        <v>35.271</v>
+        <v>36.477</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>31.284</v>
+        <v>32.405</v>
       </c>
       <c r="D36">
-        <v>0.628</v>
+        <v>0.671</v>
       </c>
       <c r="E36">
-        <v>0.793</v>
+        <v>0.819</v>
       </c>
       <c r="F36">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="G36">
-        <v>29.788</v>
+        <v>30.861</v>
       </c>
       <c r="H36">
-        <v>32.895</v>
+        <v>34.072</v>
       </c>
       <c r="I36">
-        <v>29.765</v>
+        <v>30.815</v>
       </c>
       <c r="J36">
-        <v>32.819</v>
+        <v>34.001</v>
       </c>
       <c r="K36">
-        <v>29.807</v>
+        <v>30.871</v>
       </c>
       <c r="L36">
-        <v>32.861</v>
+        <v>34.057</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>32.263</v>
+        <v>33.327</v>
       </c>
       <c r="D37">
-        <v>0.571</v>
+        <v>0.605</v>
       </c>
       <c r="E37">
-        <v>0.756</v>
+        <v>0.778</v>
       </c>
       <c r="F37">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G37">
-        <v>30.785</v>
+        <v>31.809</v>
       </c>
       <c r="H37">
-        <v>33.749</v>
+        <v>34.857</v>
       </c>
       <c r="I37">
-        <v>30.738</v>
+        <v>31.752</v>
       </c>
       <c r="J37">
-        <v>33.696</v>
+        <v>34.8</v>
       </c>
       <c r="K37">
-        <v>30.834</v>
+        <v>31.86</v>
       </c>
       <c r="L37">
-        <v>33.792</v>
+        <v>34.908</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>27.58</v>
+        <v>28.569</v>
       </c>
       <c r="D38">
-        <v>0.444</v>
+        <v>0.48</v>
       </c>
       <c r="E38">
-        <v>0.666</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F38">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G38">
-        <v>26.218</v>
+        <v>27.153</v>
       </c>
       <c r="H38">
-        <v>28.829</v>
+        <v>29.869</v>
       </c>
       <c r="I38">
-        <v>26.153</v>
+        <v>27.063</v>
       </c>
       <c r="J38">
-        <v>28.831</v>
+        <v>29.858</v>
       </c>
       <c r="K38">
-        <v>26.273</v>
+        <v>27.222</v>
       </c>
       <c r="L38">
-        <v>28.95</v>
+        <v>30.017</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>27.799</v>
+        <v>28.708</v>
       </c>
       <c r="D39">
-        <v>0.444</v>
+        <v>0.47</v>
       </c>
       <c r="E39">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F39">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G39">
-        <v>26.474</v>
+        <v>27.349</v>
       </c>
       <c r="H39">
-        <v>29.085</v>
+        <v>30.036</v>
       </c>
       <c r="I39">
-        <v>26.424</v>
+        <v>27.31</v>
       </c>
       <c r="J39">
-        <v>29.113</v>
+        <v>30.059</v>
       </c>
       <c r="K39">
-        <v>26.466</v>
+        <v>27.341</v>
       </c>
       <c r="L39">
-        <v>29.155</v>
+        <v>30.091</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>25.861</v>
+        <v>26.801</v>
       </c>
       <c r="D40">
-        <v>0.482</v>
+        <v>0.519</v>
       </c>
       <c r="E40">
-        <v>0.694</v>
+        <v>0.721</v>
       </c>
       <c r="F40">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G40">
-        <v>24.502</v>
+        <v>25.393</v>
       </c>
       <c r="H40">
-        <v>27.223</v>
+        <v>28.217</v>
       </c>
       <c r="I40">
-        <v>24.43</v>
+        <v>25.301</v>
       </c>
       <c r="J40">
-        <v>27.149</v>
+        <v>28.134</v>
       </c>
       <c r="K40">
-        <v>24.574</v>
+        <v>25.472</v>
       </c>
       <c r="L40">
-        <v>27.294</v>
+        <v>28.306</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>25.682</v>
+        <v>26.552</v>
       </c>
       <c r="D41">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="E41">
-        <v>0.7</v>
+        <v>0.721</v>
       </c>
       <c r="F41">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G41">
-        <v>24.291</v>
+        <v>25.117</v>
       </c>
       <c r="H41">
-        <v>27.034</v>
+        <v>27.945</v>
       </c>
       <c r="I41">
-        <v>24.277</v>
+        <v>25.096</v>
       </c>
       <c r="J41">
-        <v>27.016</v>
+        <v>27.94</v>
       </c>
       <c r="K41">
-        <v>24.329</v>
+        <v>25.143</v>
       </c>
       <c r="L41">
-        <v>27.068</v>
+        <v>27.987</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>25.284</v>
+        <v>26.14</v>
       </c>
       <c r="D42">
-        <v>0.501</v>
+        <v>0.527</v>
       </c>
       <c r="E42">
-        <v>0.708</v>
+        <v>0.726</v>
       </c>
       <c r="F42">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G42">
-        <v>23.867</v>
+        <v>24.687</v>
       </c>
       <c r="H42">
-        <v>26.641</v>
+        <v>27.531</v>
       </c>
       <c r="I42">
-        <v>23.83</v>
+        <v>24.647</v>
       </c>
       <c r="J42">
-        <v>26.638</v>
+        <v>27.527</v>
       </c>
       <c r="K42">
-        <v>23.9</v>
+        <v>24.722</v>
       </c>
       <c r="L42">
-        <v>26.709</v>
+        <v>27.602</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>23.273</v>
+        <v>24.068</v>
       </c>
       <c r="D43">
-        <v>0.443</v>
+        <v>0.467</v>
       </c>
       <c r="E43">
-        <v>0.666</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F43">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G43">
-        <v>22.01</v>
+        <v>22.771</v>
       </c>
       <c r="H43">
-        <v>24.619</v>
+        <v>25.45</v>
       </c>
       <c r="I43">
-        <v>21.943</v>
+        <v>22.69</v>
       </c>
       <c r="J43">
-        <v>24.548</v>
+        <v>25.392</v>
       </c>
       <c r="K43">
-        <v>22.04</v>
+        <v>22.787</v>
       </c>
       <c r="L43">
-        <v>24.644</v>
+        <v>25.488</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>22.424</v>
+        <v>23.23</v>
       </c>
       <c r="D44">
-        <v>0.459</v>
+        <v>0.486</v>
       </c>
       <c r="E44">
-        <v>0.677</v>
+        <v>0.697</v>
       </c>
       <c r="F44">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G44">
-        <v>21.099</v>
+        <v>21.866</v>
       </c>
       <c r="H44">
-        <v>23.754</v>
+        <v>24.6</v>
       </c>
       <c r="I44">
-        <v>21.064</v>
+        <v>21.825</v>
       </c>
       <c r="J44">
-        <v>23.699</v>
+        <v>24.534</v>
       </c>
       <c r="K44">
-        <v>21.152</v>
+        <v>21.929</v>
       </c>
       <c r="L44">
-        <v>23.787</v>
+        <v>24.637</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>21.902</v>
+        <v>22.637</v>
       </c>
       <c r="D45">
-        <v>0.409</v>
+        <v>0.436</v>
       </c>
       <c r="E45">
-        <v>0.639</v>
+        <v>0.66</v>
       </c>
       <c r="F45">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G45">
-        <v>20.609</v>
+        <v>21.297</v>
       </c>
       <c r="H45">
-        <v>23.114</v>
+        <v>23.886</v>
       </c>
       <c r="I45">
-        <v>20.507</v>
+        <v>21.185</v>
       </c>
       <c r="J45">
-        <v>23.111</v>
+        <v>23.857</v>
       </c>
       <c r="K45">
-        <v>20.652</v>
+        <v>21.371</v>
       </c>
       <c r="L45">
-        <v>23.257</v>
+        <v>24.043</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>21.103</v>
+        <v>21.837</v>
       </c>
       <c r="D46">
-        <v>0.448</v>
+        <v>0.474</v>
       </c>
       <c r="E46">
-        <v>0.669</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F46">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G46">
-        <v>19.78</v>
+        <v>20.474</v>
       </c>
       <c r="H46">
-        <v>22.403</v>
+        <v>23.172</v>
       </c>
       <c r="I46">
-        <v>19.713</v>
+        <v>20.386</v>
       </c>
       <c r="J46">
-        <v>22.374</v>
+        <v>23.149</v>
       </c>
       <c r="K46">
-        <v>19.821</v>
+        <v>20.511</v>
       </c>
       <c r="L46">
-        <v>22.482</v>
+        <v>23.274</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>19.384</v>
+        <v>20.043</v>
       </c>
       <c r="D47">
-        <v>0.354</v>
+        <v>0.373</v>
       </c>
       <c r="E47">
-        <v>0.595</v>
+        <v>0.61</v>
       </c>
       <c r="F47">
         <v>0.019</v>
       </c>
       <c r="G47">
-        <v>18.229</v>
+        <v>18.86</v>
       </c>
       <c r="H47">
-        <v>20.562</v>
+        <v>21.253</v>
       </c>
       <c r="I47">
-        <v>18.206</v>
+        <v>18.808</v>
       </c>
       <c r="J47">
-        <v>20.536</v>
+        <v>21.233</v>
       </c>
       <c r="K47">
-        <v>18.244</v>
+        <v>18.866</v>
       </c>
       <c r="L47">
-        <v>20.574</v>
+        <v>21.291</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>19.233</v>
+        <v>19.88</v>
       </c>
       <c r="D48">
-        <v>0.422</v>
+        <v>0.436</v>
       </c>
       <c r="E48">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="F48">
         <v>0.021</v>
       </c>
       <c r="G48">
-        <v>17.91</v>
+        <v>18.537</v>
       </c>
       <c r="H48">
-        <v>20.456</v>
+        <v>21.124</v>
       </c>
       <c r="I48">
-        <v>17.946</v>
+        <v>18.573</v>
       </c>
       <c r="J48">
-        <v>20.484</v>
+        <v>21.165</v>
       </c>
       <c r="K48">
-        <v>17.932</v>
+        <v>18.545</v>
       </c>
       <c r="L48">
-        <v>20.47</v>
+        <v>21.138</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>17.46</v>
+        <v>18.081</v>
       </c>
       <c r="D49">
-        <v>0.315</v>
+        <v>0.332</v>
       </c>
       <c r="E49">
-        <v>0.5610000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="F49">
         <v>0.018</v>
       </c>
       <c r="G49">
-        <v>16.349</v>
+        <v>16.945</v>
       </c>
       <c r="H49">
-        <v>18.55</v>
+        <v>19.203</v>
       </c>
       <c r="I49">
-        <v>16.436</v>
+        <v>16.993</v>
       </c>
       <c r="J49">
-        <v>18.532</v>
+        <v>19.174</v>
       </c>
       <c r="K49">
-        <v>16.378</v>
+        <v>16.98</v>
       </c>
       <c r="L49">
-        <v>18.474</v>
+        <v>19.161</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>243.364</v>
+        <v>245.632</v>
       </c>
       <c r="D2">
-        <v>5.128</v>
+        <v>5.731</v>
       </c>
       <c r="E2">
-        <v>2.265</v>
+        <v>2.394</v>
       </c>
       <c r="F2">
-        <v>0.07199999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="G2">
-        <v>238.996</v>
+        <v>241.003</v>
       </c>
       <c r="H2">
-        <v>247.873</v>
+        <v>250.387</v>
       </c>
       <c r="I2">
-        <v>239.039</v>
+        <v>241.079</v>
       </c>
       <c r="J2">
-        <v>247.649</v>
+        <v>250.037</v>
       </c>
       <c r="K2">
-        <v>239.15</v>
+        <v>241.29</v>
       </c>
       <c r="L2">
-        <v>247.76</v>
+        <v>250.249</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>163.797</v>
+        <v>165.399</v>
       </c>
       <c r="D3">
-        <v>2.955</v>
+        <v>3.152</v>
       </c>
       <c r="E3">
-        <v>1.719</v>
+        <v>1.775</v>
       </c>
       <c r="F3">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="G3">
-        <v>160.356</v>
+        <v>161.842</v>
       </c>
       <c r="H3">
-        <v>167.095</v>
+        <v>168.802</v>
       </c>
       <c r="I3">
-        <v>160.2</v>
+        <v>161.558</v>
       </c>
       <c r="J3">
-        <v>167.039</v>
+        <v>168.681</v>
       </c>
       <c r="K3">
-        <v>160.484</v>
+        <v>162.04</v>
       </c>
       <c r="L3">
-        <v>167.323</v>
+        <v>169.163</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>108.975</v>
+        <v>110.272</v>
       </c>
       <c r="D4">
-        <v>2.156</v>
+        <v>2.347</v>
       </c>
       <c r="E4">
-        <v>1.468</v>
+        <v>1.532</v>
       </c>
       <c r="F4">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="G4">
-        <v>106.003</v>
+        <v>107.183</v>
       </c>
       <c r="H4">
-        <v>111.759</v>
+        <v>113.188</v>
       </c>
       <c r="I4">
-        <v>106.038</v>
+        <v>107.217</v>
       </c>
       <c r="J4">
-        <v>111.729</v>
+        <v>113.099</v>
       </c>
       <c r="K4">
-        <v>106.127</v>
+        <v>107.358</v>
       </c>
       <c r="L4">
-        <v>111.819</v>
+        <v>113.24</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>77.69199999999999</v>
+        <v>78.464</v>
       </c>
       <c r="D5">
-        <v>2.524</v>
+        <v>2.548</v>
       </c>
       <c r="E5">
-        <v>1.589</v>
+        <v>1.596</v>
       </c>
       <c r="F5">
         <v>0.05</v>
       </c>
       <c r="G5">
-        <v>74.429</v>
+        <v>75.188</v>
       </c>
       <c r="H5">
-        <v>80.65600000000001</v>
+        <v>81.446</v>
       </c>
       <c r="I5">
-        <v>74.20999999999999</v>
+        <v>75.01300000000001</v>
       </c>
       <c r="J5">
-        <v>80.443</v>
+        <v>81.28</v>
       </c>
       <c r="K5">
-        <v>74.791</v>
+        <v>75.5</v>
       </c>
       <c r="L5">
-        <v>81.02500000000001</v>
+        <v>81.767</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>59.668</v>
+        <v>60.469</v>
       </c>
       <c r="D6">
-        <v>0.994</v>
+        <v>1.028</v>
       </c>
       <c r="E6">
-        <v>0.997</v>
+        <v>1.014</v>
       </c>
       <c r="F6">
         <v>0.032</v>
       </c>
       <c r="G6">
-        <v>57.764</v>
+        <v>58.548</v>
       </c>
       <c r="H6">
-        <v>61.672</v>
+        <v>62.523</v>
       </c>
       <c r="I6">
-        <v>57.748</v>
+        <v>58.55</v>
       </c>
       <c r="J6">
-        <v>61.699</v>
+        <v>62.578</v>
       </c>
       <c r="K6">
-        <v>57.688</v>
+        <v>58.427</v>
       </c>
       <c r="L6">
-        <v>61.639</v>
+        <v>62.455</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>48.589</v>
+        <v>49.306</v>
       </c>
       <c r="D7">
-        <v>0.891</v>
+        <v>0.946</v>
       </c>
       <c r="E7">
-        <v>0.944</v>
+        <v>0.973</v>
       </c>
       <c r="F7">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="G7">
-        <v>46.761</v>
+        <v>47.421</v>
       </c>
       <c r="H7">
-        <v>50.461</v>
+        <v>51.234</v>
       </c>
       <c r="I7">
-        <v>46.776</v>
+        <v>47.381</v>
       </c>
       <c r="J7">
-        <v>50.388</v>
+        <v>51.166</v>
       </c>
       <c r="K7">
-        <v>46.813</v>
+        <v>47.467</v>
       </c>
       <c r="L7">
-        <v>50.425</v>
+        <v>51.251</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>41.819</v>
+        <v>42.718</v>
       </c>
       <c r="D8">
-        <v>0.773</v>
+        <v>0.887</v>
       </c>
       <c r="E8">
-        <v>0.879</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F8">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="G8">
-        <v>40.136</v>
+        <v>40.93</v>
       </c>
       <c r="H8">
-        <v>43.583</v>
+        <v>44.623</v>
       </c>
       <c r="I8">
-        <v>40.061</v>
+        <v>40.686</v>
       </c>
       <c r="J8">
-        <v>43.538</v>
+        <v>44.58</v>
       </c>
       <c r="K8">
-        <v>40.141</v>
+        <v>40.915</v>
       </c>
       <c r="L8">
-        <v>43.618</v>
+        <v>44.809</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>36.247</v>
+        <v>37.092</v>
       </c>
       <c r="D9">
-        <v>0.6909999999999999</v>
+        <v>0.776</v>
       </c>
       <c r="E9">
-        <v>0.831</v>
+        <v>0.881</v>
       </c>
       <c r="F9">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="G9">
-        <v>34.599</v>
+        <v>35.344</v>
       </c>
       <c r="H9">
-        <v>37.857</v>
+        <v>38.796</v>
       </c>
       <c r="I9">
-        <v>34.566</v>
+        <v>35.305</v>
       </c>
       <c r="J9">
-        <v>37.859</v>
+        <v>38.735</v>
       </c>
       <c r="K9">
-        <v>34.616</v>
+        <v>35.427</v>
       </c>
       <c r="L9">
-        <v>37.909</v>
+        <v>38.857</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>32.371</v>
+        <v>33.086</v>
       </c>
       <c r="D10">
-        <v>0.586</v>
+        <v>0.643</v>
       </c>
       <c r="E10">
-        <v>0.765</v>
+        <v>0.802</v>
       </c>
       <c r="F10">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G10">
-        <v>30.859</v>
+        <v>31.505</v>
       </c>
       <c r="H10">
-        <v>33.859</v>
+        <v>34.647</v>
       </c>
       <c r="I10">
-        <v>30.83</v>
+        <v>31.495</v>
       </c>
       <c r="J10">
-        <v>33.851</v>
+        <v>34.625</v>
       </c>
       <c r="K10">
-        <v>30.879</v>
+        <v>31.538</v>
       </c>
       <c r="L10">
-        <v>33.9</v>
+        <v>34.667</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>31.212</v>
+        <v>31.907</v>
       </c>
       <c r="D11">
-        <v>0.528</v>
+        <v>0.575</v>
       </c>
       <c r="E11">
-        <v>0.726</v>
+        <v>0.758</v>
       </c>
       <c r="F11">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G11">
-        <v>29.761</v>
+        <v>30.399</v>
       </c>
       <c r="H11">
-        <v>32.609</v>
+        <v>33.37</v>
       </c>
       <c r="I11">
-        <v>29.751</v>
+        <v>30.341</v>
       </c>
       <c r="J11">
-        <v>32.566</v>
+        <v>33.309</v>
       </c>
       <c r="K11">
-        <v>29.831</v>
+        <v>30.482</v>
       </c>
       <c r="L11">
-        <v>32.646</v>
+        <v>33.45</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>29.098</v>
+        <v>29.861</v>
       </c>
       <c r="D12">
-        <v>0.592</v>
+        <v>0.639</v>
       </c>
       <c r="E12">
-        <v>0.769</v>
+        <v>0.799</v>
       </c>
       <c r="F12">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G12">
-        <v>27.502</v>
+        <v>28.206</v>
       </c>
       <c r="H12">
-        <v>30.517</v>
+        <v>31.339</v>
       </c>
       <c r="I12">
-        <v>27.386</v>
+        <v>28.157</v>
       </c>
       <c r="J12">
-        <v>30.516</v>
+        <v>31.26</v>
       </c>
       <c r="K12">
-        <v>27.591</v>
+        <v>28.373</v>
       </c>
       <c r="L12">
-        <v>30.72</v>
+        <v>31.476</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>29.876</v>
+        <v>30.567</v>
       </c>
       <c r="D13">
-        <v>0.53</v>
+        <v>0.575</v>
       </c>
       <c r="E13">
-        <v>0.728</v>
+        <v>0.758</v>
       </c>
       <c r="F13">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G13">
-        <v>28.406</v>
+        <v>29.044</v>
       </c>
       <c r="H13">
-        <v>31.259</v>
+        <v>32.015</v>
       </c>
       <c r="I13">
-        <v>28.345</v>
+        <v>29.003</v>
       </c>
       <c r="J13">
-        <v>31.24</v>
+        <v>31.988</v>
       </c>
       <c r="K13">
-        <v>28.469</v>
+        <v>29.109</v>
       </c>
       <c r="L13">
-        <v>31.364</v>
+        <v>32.094</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>25.568</v>
+        <v>26.179</v>
       </c>
       <c r="D14">
-        <v>0.396</v>
+        <v>0.454</v>
       </c>
       <c r="E14">
-        <v>0.629</v>
+        <v>0.674</v>
       </c>
       <c r="F14">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G14">
-        <v>24.327</v>
+        <v>24.856</v>
       </c>
       <c r="H14">
-        <v>26.793</v>
+        <v>27.497</v>
       </c>
       <c r="I14">
-        <v>24.35</v>
+        <v>24.85</v>
       </c>
       <c r="J14">
-        <v>26.707</v>
+        <v>27.451</v>
       </c>
       <c r="K14">
-        <v>24.421</v>
+        <v>24.904</v>
       </c>
       <c r="L14">
-        <v>26.778</v>
+        <v>27.504</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>25.703</v>
+        <v>26.297</v>
       </c>
       <c r="D15">
-        <v>0.421</v>
+        <v>0.473</v>
       </c>
       <c r="E15">
-        <v>0.649</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F15">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G15">
-        <v>24.44</v>
+        <v>24.971</v>
       </c>
       <c r="H15">
-        <v>26.984</v>
+        <v>27.667</v>
       </c>
       <c r="I15">
-        <v>24.47</v>
+        <v>24.985</v>
       </c>
       <c r="J15">
-        <v>26.958</v>
+        <v>27.655</v>
       </c>
       <c r="K15">
-        <v>24.457</v>
+        <v>24.961</v>
       </c>
       <c r="L15">
-        <v>26.945</v>
+        <v>27.631</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>24.038</v>
+        <v>24.677</v>
       </c>
       <c r="D16">
-        <v>0.47</v>
+        <v>0.525</v>
       </c>
       <c r="E16">
-        <v>0.6850000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="F16">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G16">
-        <v>22.635</v>
+        <v>23.206</v>
       </c>
       <c r="H16">
-        <v>25.322</v>
+        <v>26.046</v>
       </c>
       <c r="I16">
-        <v>22.578</v>
+        <v>23.157</v>
       </c>
       <c r="J16">
-        <v>25.309</v>
+        <v>26.03</v>
       </c>
       <c r="K16">
-        <v>22.707</v>
+        <v>23.272</v>
       </c>
       <c r="L16">
-        <v>25.438</v>
+        <v>26.146</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>23.798</v>
+        <v>24.241</v>
       </c>
       <c r="D17">
-        <v>0.414</v>
+        <v>0.445</v>
       </c>
       <c r="E17">
-        <v>0.644</v>
+        <v>0.667</v>
       </c>
       <c r="F17">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G17">
-        <v>22.488</v>
+        <v>22.894</v>
       </c>
       <c r="H17">
-        <v>25.01</v>
+        <v>25.509</v>
       </c>
       <c r="I17">
-        <v>22.49</v>
+        <v>22.909</v>
       </c>
       <c r="J17">
-        <v>25.008</v>
+        <v>25.492</v>
       </c>
       <c r="K17">
-        <v>22.539</v>
+        <v>22.95</v>
       </c>
       <c r="L17">
-        <v>25.057</v>
+        <v>25.534</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>23.407</v>
+        <v>24.012</v>
       </c>
       <c r="D18">
-        <v>0.438</v>
+        <v>0.476</v>
       </c>
       <c r="E18">
-        <v>0.662</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F18">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G18">
-        <v>22.097</v>
+        <v>22.645</v>
       </c>
       <c r="H18">
-        <v>24.691</v>
+        <v>25.349</v>
       </c>
       <c r="I18">
-        <v>22.069</v>
+        <v>22.618</v>
       </c>
       <c r="J18">
-        <v>24.614</v>
+        <v>25.291</v>
       </c>
       <c r="K18">
-        <v>22.187</v>
+        <v>22.718</v>
       </c>
       <c r="L18">
-        <v>24.732</v>
+        <v>25.391</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>21.604</v>
+        <v>22.046</v>
       </c>
       <c r="D19">
-        <v>0.392</v>
+        <v>0.412</v>
       </c>
       <c r="E19">
-        <v>0.626</v>
+        <v>0.642</v>
       </c>
       <c r="F19">
         <v>0.02</v>
       </c>
       <c r="G19">
-        <v>20.324</v>
+        <v>20.744</v>
       </c>
       <c r="H19">
-        <v>22.777</v>
+        <v>23.259</v>
       </c>
       <c r="I19">
-        <v>20.275</v>
+        <v>20.729</v>
       </c>
       <c r="J19">
-        <v>22.75</v>
+        <v>23.226</v>
       </c>
       <c r="K19">
-        <v>20.405</v>
+        <v>20.821</v>
       </c>
       <c r="L19">
-        <v>22.88</v>
+        <v>23.318</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>20.816</v>
+        <v>21.673</v>
       </c>
       <c r="D20">
-        <v>0.36</v>
+        <v>0.741</v>
       </c>
       <c r="E20">
-        <v>0.6</v>
+        <v>0.861</v>
       </c>
       <c r="F20">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="G20">
-        <v>19.626</v>
+        <v>19.974</v>
       </c>
       <c r="H20">
-        <v>21.976</v>
+        <v>23.348</v>
       </c>
       <c r="I20">
-        <v>19.523</v>
+        <v>19.698</v>
       </c>
       <c r="J20">
-        <v>21.961</v>
+        <v>23.205</v>
       </c>
       <c r="K20">
-        <v>19.657</v>
+        <v>20.129</v>
       </c>
       <c r="L20">
-        <v>22.095</v>
+        <v>23.635</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>20.293</v>
+        <v>20.777</v>
       </c>
       <c r="D21">
-        <v>0.371</v>
+        <v>0.408</v>
       </c>
       <c r="E21">
-        <v>0.609</v>
+        <v>0.639</v>
       </c>
       <c r="F21">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G21">
-        <v>19.026</v>
+        <v>19.461</v>
       </c>
       <c r="H21">
-        <v>21.412</v>
+        <v>21.965</v>
       </c>
       <c r="I21">
-        <v>18.969</v>
+        <v>19.423</v>
       </c>
       <c r="J21">
-        <v>21.427</v>
+        <v>21.953</v>
       </c>
       <c r="K21">
-        <v>19.085</v>
+        <v>19.537</v>
       </c>
       <c r="L21">
-        <v>21.543</v>
+        <v>22.067</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>19.546</v>
+        <v>19.881</v>
       </c>
       <c r="D22">
-        <v>0.411</v>
+        <v>0.435</v>
       </c>
       <c r="E22">
-        <v>0.641</v>
+        <v>0.66</v>
       </c>
       <c r="F22">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G22">
-        <v>18.305</v>
+        <v>18.612</v>
       </c>
       <c r="H22">
-        <v>20.818</v>
+        <v>21.198</v>
       </c>
       <c r="I22">
-        <v>18.305</v>
+        <v>18.583</v>
       </c>
       <c r="J22">
-        <v>20.785</v>
+        <v>21.156</v>
       </c>
       <c r="K22">
-        <v>18.322</v>
+        <v>18.631</v>
       </c>
       <c r="L22">
-        <v>20.803</v>
+        <v>21.204</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>17.941</v>
+        <v>18.293</v>
       </c>
       <c r="D23">
-        <v>0.309</v>
+        <v>0.32</v>
       </c>
       <c r="E23">
-        <v>0.556</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F23">
         <v>0.018</v>
       </c>
       <c r="G23">
-        <v>16.888</v>
+        <v>17.224</v>
       </c>
       <c r="H23">
-        <v>19.067</v>
+        <v>19.441</v>
       </c>
       <c r="I23">
-        <v>16.843</v>
+        <v>17.196</v>
       </c>
       <c r="J23">
-        <v>19.11</v>
+        <v>19.445</v>
       </c>
       <c r="K23">
-        <v>16.808</v>
+        <v>17.18</v>
       </c>
       <c r="L23">
-        <v>19.075</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>17.784</v>
+        <v>17.985</v>
       </c>
       <c r="D24">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="E24">
-        <v>0.606</v>
+        <v>0.612</v>
       </c>
       <c r="F24">
         <v>0.019</v>
       </c>
       <c r="G24">
-        <v>16.599</v>
+        <v>16.786</v>
       </c>
       <c r="H24">
-        <v>18.972</v>
+        <v>19.186</v>
       </c>
       <c r="I24">
-        <v>16.584</v>
+        <v>16.789</v>
       </c>
       <c r="J24">
-        <v>19.012</v>
+        <v>19.192</v>
       </c>
       <c r="K24">
-        <v>16.557</v>
+        <v>16.779</v>
       </c>
       <c r="L24">
-        <v>18.986</v>
+        <v>19.181</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>16.199</v>
+        <v>16.462</v>
       </c>
       <c r="D25">
-        <v>0.256</v>
+        <v>0.271</v>
       </c>
       <c r="E25">
-        <v>0.506</v>
+        <v>0.52</v>
       </c>
       <c r="F25">
         <v>0.016</v>
       </c>
       <c r="G25">
-        <v>15.193</v>
+        <v>15.43</v>
       </c>
       <c r="H25">
-        <v>17.177</v>
+        <v>17.468</v>
       </c>
       <c r="I25">
-        <v>15.133</v>
+        <v>15.345</v>
       </c>
       <c r="J25">
-        <v>17.098</v>
+        <v>17.413</v>
       </c>
       <c r="K25">
-        <v>15.286</v>
+        <v>15.498</v>
       </c>
       <c r="L25">
-        <v>17.251</v>
+        <v>17.566</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>271.688</v>
+        <v>274.236</v>
       </c>
       <c r="D26">
-        <v>6.249</v>
+        <v>6.982</v>
       </c>
       <c r="E26">
-        <v>2.5</v>
+        <v>2.642</v>
       </c>
       <c r="F26">
-        <v>0.079</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G26">
-        <v>266.884</v>
+        <v>269.113</v>
       </c>
       <c r="H26">
-        <v>276.683</v>
+        <v>279.47</v>
       </c>
       <c r="I26">
-        <v>266.827</v>
+        <v>269.102</v>
       </c>
       <c r="J26">
-        <v>276.449</v>
+        <v>279.38</v>
       </c>
       <c r="K26">
-        <v>267.022</v>
+        <v>269.147</v>
       </c>
       <c r="L26">
-        <v>276.644</v>
+        <v>279.426</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>182.813</v>
+        <v>184.595</v>
       </c>
       <c r="D27">
-        <v>3.953</v>
+        <v>4.237</v>
       </c>
       <c r="E27">
-        <v>1.988</v>
+        <v>2.058</v>
       </c>
       <c r="F27">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="G27">
-        <v>178.942</v>
+        <v>180.594</v>
       </c>
       <c r="H27">
-        <v>186.737</v>
+        <v>188.663</v>
       </c>
       <c r="I27">
-        <v>178.639</v>
+        <v>180.308</v>
       </c>
       <c r="J27">
-        <v>186.64</v>
+        <v>188.566</v>
       </c>
       <c r="K27">
-        <v>179.013</v>
+        <v>180.657</v>
       </c>
       <c r="L27">
-        <v>187.013</v>
+        <v>188.915</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>121.591</v>
+        <v>123.027</v>
       </c>
       <c r="D28">
-        <v>2.545</v>
+        <v>2.885</v>
       </c>
       <c r="E28">
-        <v>1.595</v>
+        <v>1.699</v>
       </c>
       <c r="F28">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="G28">
-        <v>118.501</v>
+        <v>119.766</v>
       </c>
       <c r="H28">
-        <v>124.756</v>
+        <v>126.425</v>
       </c>
       <c r="I28">
-        <v>118.337</v>
+        <v>119.354</v>
       </c>
       <c r="J28">
-        <v>124.657</v>
+        <v>126.323</v>
       </c>
       <c r="K28">
-        <v>118.562</v>
+        <v>119.8</v>
       </c>
       <c r="L28">
-        <v>124.882</v>
+        <v>126.768</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>86.646</v>
+        <v>87.504</v>
       </c>
       <c r="D29">
-        <v>3.227</v>
+        <v>3.291</v>
       </c>
       <c r="E29">
-        <v>1.796</v>
+        <v>1.814</v>
       </c>
       <c r="F29">
         <v>0.057</v>
       </c>
       <c r="G29">
-        <v>83.14100000000001</v>
+        <v>83.974</v>
       </c>
       <c r="H29">
-        <v>90.182</v>
+        <v>91.08499999999999</v>
       </c>
       <c r="I29">
-        <v>82.693</v>
+        <v>83.506</v>
       </c>
       <c r="J29">
-        <v>89.92400000000001</v>
+        <v>90.822</v>
       </c>
       <c r="K29">
-        <v>83.383</v>
+        <v>84.211</v>
       </c>
       <c r="L29">
-        <v>90.614</v>
+        <v>91.527</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>66.613</v>
+        <v>67.52</v>
       </c>
       <c r="D30">
-        <v>1.296</v>
+        <v>1.344</v>
       </c>
       <c r="E30">
-        <v>1.138</v>
+        <v>1.159</v>
       </c>
       <c r="F30">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="G30">
-        <v>64.44199999999999</v>
+        <v>65.3</v>
       </c>
       <c r="H30">
-        <v>68.904</v>
+        <v>69.84399999999999</v>
       </c>
       <c r="I30">
-        <v>64.3</v>
+        <v>65.205</v>
       </c>
       <c r="J30">
-        <v>68.89100000000001</v>
+        <v>69.873</v>
       </c>
       <c r="K30">
-        <v>64.39400000000001</v>
+        <v>65.21899999999999</v>
       </c>
       <c r="L30">
-        <v>68.985</v>
+        <v>69.887</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>54.278</v>
+        <v>55.079</v>
       </c>
       <c r="D31">
-        <v>1.103</v>
+        <v>1.146</v>
       </c>
       <c r="E31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="F31">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="G31">
-        <v>52.181</v>
+        <v>52.938</v>
       </c>
       <c r="H31">
-        <v>56.298</v>
+        <v>57.135</v>
       </c>
       <c r="I31">
-        <v>52.134</v>
+        <v>52.913</v>
       </c>
       <c r="J31">
-        <v>56.243</v>
+        <v>57.052</v>
       </c>
       <c r="K31">
-        <v>52.274</v>
+        <v>53.063</v>
       </c>
       <c r="L31">
-        <v>56.383</v>
+        <v>57.202</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>46.702</v>
+        <v>47.727</v>
       </c>
       <c r="D32">
-        <v>0.997</v>
+        <v>1.16</v>
       </c>
       <c r="E32">
-        <v>0.999</v>
+        <v>1.077</v>
       </c>
       <c r="F32">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="G32">
-        <v>44.762</v>
+        <v>45.611</v>
       </c>
       <c r="H32">
-        <v>48.676</v>
+        <v>49.832</v>
       </c>
       <c r="I32">
-        <v>44.758</v>
+        <v>45.522</v>
       </c>
       <c r="J32">
-        <v>48.691</v>
+        <v>49.878</v>
       </c>
       <c r="K32">
-        <v>44.73</v>
+        <v>45.57</v>
       </c>
       <c r="L32">
-        <v>48.663</v>
+        <v>49.926</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>40.493</v>
+        <v>41.435</v>
       </c>
       <c r="D33">
-        <v>0.824</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E33">
-        <v>0.908</v>
+        <v>0.967</v>
       </c>
       <c r="F33">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="G33">
-        <v>38.641</v>
+        <v>39.464</v>
       </c>
       <c r="H33">
-        <v>42.199</v>
+        <v>43.256</v>
       </c>
       <c r="I33">
-        <v>38.646</v>
+        <v>39.498</v>
       </c>
       <c r="J33">
-        <v>42.202</v>
+        <v>43.333</v>
       </c>
       <c r="K33">
-        <v>38.71</v>
+        <v>39.463</v>
       </c>
       <c r="L33">
-        <v>42.267</v>
+        <v>43.298</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>36.168</v>
+        <v>36.966</v>
       </c>
       <c r="D34">
-        <v>0.65</v>
+        <v>0.713</v>
       </c>
       <c r="E34">
-        <v>0.806</v>
+        <v>0.844</v>
       </c>
       <c r="F34">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="G34">
-        <v>34.518</v>
+        <v>35.245</v>
       </c>
       <c r="H34">
-        <v>37.678</v>
+        <v>38.555</v>
       </c>
       <c r="I34">
-        <v>34.458</v>
+        <v>35.258</v>
       </c>
       <c r="J34">
-        <v>37.656</v>
+        <v>38.573</v>
       </c>
       <c r="K34">
-        <v>34.609</v>
+        <v>35.292</v>
       </c>
       <c r="L34">
-        <v>37.808</v>
+        <v>38.607</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>34.853</v>
+        <v>35.628</v>
       </c>
       <c r="D35">
-        <v>0.631</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E35">
-        <v>0.794</v>
+        <v>0.829</v>
       </c>
       <c r="F35">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="G35">
-        <v>33.252</v>
+        <v>33.965</v>
       </c>
       <c r="H35">
-        <v>36.365</v>
+        <v>37.215</v>
       </c>
       <c r="I35">
-        <v>33.184</v>
+        <v>33.881</v>
       </c>
       <c r="J35">
-        <v>36.451</v>
+        <v>37.246</v>
       </c>
       <c r="K35">
-        <v>33.211</v>
+        <v>33.972</v>
       </c>
       <c r="L35">
-        <v>36.477</v>
+        <v>37.336</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>32.405</v>
+        <v>33.254</v>
       </c>
       <c r="D36">
-        <v>0.671</v>
+        <v>0.721</v>
       </c>
       <c r="E36">
-        <v>0.819</v>
+        <v>0.849</v>
       </c>
       <c r="F36">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="G36">
-        <v>30.861</v>
+        <v>31.657</v>
       </c>
       <c r="H36">
-        <v>34.072</v>
+        <v>34.986</v>
       </c>
       <c r="I36">
-        <v>30.815</v>
+        <v>31.611</v>
       </c>
       <c r="J36">
-        <v>34.001</v>
+        <v>34.92</v>
       </c>
       <c r="K36">
-        <v>30.871</v>
+        <v>31.656</v>
       </c>
       <c r="L36">
-        <v>34.057</v>
+        <v>34.964</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>33.327</v>
+        <v>34.096</v>
       </c>
       <c r="D37">
-        <v>0.605</v>
+        <v>0.656</v>
       </c>
       <c r="E37">
-        <v>0.778</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F37">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="G37">
-        <v>31.809</v>
+        <v>32.526</v>
       </c>
       <c r="H37">
-        <v>34.857</v>
+        <v>35.701</v>
       </c>
       <c r="I37">
-        <v>31.752</v>
+        <v>32.479</v>
       </c>
       <c r="J37">
-        <v>34.8</v>
+        <v>35.64</v>
       </c>
       <c r="K37">
-        <v>31.86</v>
+        <v>32.57</v>
       </c>
       <c r="L37">
-        <v>34.908</v>
+        <v>35.731</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>28.569</v>
+        <v>29.246</v>
       </c>
       <c r="D38">
-        <v>0.48</v>
+        <v>0.535</v>
       </c>
       <c r="E38">
-        <v>0.6929999999999999</v>
+        <v>0.732</v>
       </c>
       <c r="F38">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G38">
-        <v>27.153</v>
+        <v>27.77</v>
       </c>
       <c r="H38">
-        <v>29.869</v>
+        <v>30.638</v>
       </c>
       <c r="I38">
-        <v>27.063</v>
+        <v>27.681</v>
       </c>
       <c r="J38">
-        <v>29.858</v>
+        <v>30.641</v>
       </c>
       <c r="K38">
-        <v>27.222</v>
+        <v>27.81</v>
       </c>
       <c r="L38">
-        <v>30.017</v>
+        <v>30.769</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>28.708</v>
+        <v>29.39</v>
       </c>
       <c r="D39">
-        <v>0.47</v>
+        <v>0.535</v>
       </c>
       <c r="E39">
-        <v>0.6850000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="F39">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G39">
-        <v>27.349</v>
+        <v>27.918</v>
       </c>
       <c r="H39">
-        <v>30.036</v>
+        <v>30.786</v>
       </c>
       <c r="I39">
-        <v>27.31</v>
+        <v>27.819</v>
       </c>
       <c r="J39">
-        <v>30.059</v>
+        <v>30.805</v>
       </c>
       <c r="K39">
-        <v>27.341</v>
+        <v>27.936</v>
       </c>
       <c r="L39">
-        <v>30.091</v>
+        <v>30.922</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>26.801</v>
+        <v>27.527</v>
       </c>
       <c r="D40">
-        <v>0.519</v>
+        <v>0.576</v>
       </c>
       <c r="E40">
-        <v>0.721</v>
+        <v>0.759</v>
       </c>
       <c r="F40">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G40">
-        <v>25.393</v>
+        <v>26.028</v>
       </c>
       <c r="H40">
-        <v>28.217</v>
+        <v>29.003</v>
       </c>
       <c r="I40">
-        <v>25.301</v>
+        <v>26.033</v>
       </c>
       <c r="J40">
-        <v>28.134</v>
+        <v>28.927</v>
       </c>
       <c r="K40">
-        <v>25.472</v>
+        <v>26.115</v>
       </c>
       <c r="L40">
-        <v>28.306</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>26.552</v>
+        <v>27.049</v>
       </c>
       <c r="D41">
-        <v>0.52</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E41">
-        <v>0.721</v>
+        <v>0.754</v>
       </c>
       <c r="F41">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G41">
-        <v>25.117</v>
+        <v>25.556</v>
       </c>
       <c r="H41">
-        <v>27.945</v>
+        <v>28.511</v>
       </c>
       <c r="I41">
-        <v>25.096</v>
+        <v>25.563</v>
       </c>
       <c r="J41">
-        <v>27.94</v>
+        <v>28.438</v>
       </c>
       <c r="K41">
-        <v>25.143</v>
+        <v>25.645</v>
       </c>
       <c r="L41">
-        <v>27.987</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>26.14</v>
+        <v>26.811</v>
       </c>
       <c r="D42">
-        <v>0.527</v>
+        <v>0.577</v>
       </c>
       <c r="E42">
-        <v>0.726</v>
+        <v>0.759</v>
       </c>
       <c r="F42">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G42">
-        <v>24.687</v>
+        <v>25.298</v>
       </c>
       <c r="H42">
-        <v>27.531</v>
+        <v>28.275</v>
       </c>
       <c r="I42">
-        <v>24.647</v>
+        <v>25.248</v>
       </c>
       <c r="J42">
-        <v>27.527</v>
+        <v>28.227</v>
       </c>
       <c r="K42">
-        <v>24.722</v>
+        <v>25.371</v>
       </c>
       <c r="L42">
-        <v>27.602</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>24.068</v>
+        <v>24.561</v>
       </c>
       <c r="D43">
-        <v>0.467</v>
+        <v>0.501</v>
       </c>
       <c r="E43">
-        <v>0.6830000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="F43">
         <v>0.022</v>
       </c>
       <c r="G43">
-        <v>22.771</v>
+        <v>23.227</v>
       </c>
       <c r="H43">
-        <v>25.45</v>
+        <v>26.001</v>
       </c>
       <c r="I43">
-        <v>22.69</v>
+        <v>23.128</v>
       </c>
       <c r="J43">
-        <v>25.392</v>
+        <v>25.96</v>
       </c>
       <c r="K43">
-        <v>22.787</v>
+        <v>23.215</v>
       </c>
       <c r="L43">
-        <v>25.488</v>
+        <v>26.047</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>23.23</v>
+        <v>24.162</v>
       </c>
       <c r="D44">
-        <v>0.486</v>
+        <v>0.978</v>
       </c>
       <c r="E44">
-        <v>0.697</v>
+        <v>0.989</v>
       </c>
       <c r="F44">
-        <v>0.022</v>
+        <v>0.031</v>
       </c>
       <c r="G44">
-        <v>21.866</v>
+        <v>22.278</v>
       </c>
       <c r="H44">
-        <v>24.6</v>
+        <v>26.155</v>
       </c>
       <c r="I44">
-        <v>21.825</v>
+        <v>21.913</v>
       </c>
       <c r="J44">
-        <v>24.534</v>
+        <v>25.914</v>
       </c>
       <c r="K44">
-        <v>21.929</v>
+        <v>22.465</v>
       </c>
       <c r="L44">
-        <v>24.637</v>
+        <v>26.465</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>22.637</v>
+        <v>23.186</v>
       </c>
       <c r="D45">
-        <v>0.436</v>
+        <v>0.488</v>
       </c>
       <c r="E45">
-        <v>0.66</v>
+        <v>0.699</v>
       </c>
       <c r="F45">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G45">
-        <v>21.297</v>
+        <v>21.765</v>
       </c>
       <c r="H45">
-        <v>23.886</v>
+        <v>24.504</v>
       </c>
       <c r="I45">
-        <v>21.185</v>
+        <v>21.715</v>
       </c>
       <c r="J45">
-        <v>23.857</v>
+        <v>24.451</v>
       </c>
       <c r="K45">
-        <v>21.371</v>
+        <v>21.869</v>
       </c>
       <c r="L45">
-        <v>24.043</v>
+        <v>24.605</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>21.837</v>
+        <v>22.221</v>
       </c>
       <c r="D46">
-        <v>0.474</v>
+        <v>0.504</v>
       </c>
       <c r="E46">
-        <v>0.6879999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="F46">
         <v>0.022</v>
       </c>
       <c r="G46">
-        <v>20.474</v>
+        <v>20.806</v>
       </c>
       <c r="H46">
-        <v>23.172</v>
+        <v>23.589</v>
       </c>
       <c r="I46">
-        <v>20.386</v>
+        <v>20.733</v>
       </c>
       <c r="J46">
-        <v>23.149</v>
+        <v>23.552</v>
       </c>
       <c r="K46">
-        <v>20.511</v>
+        <v>20.867</v>
       </c>
       <c r="L46">
-        <v>23.274</v>
+        <v>23.685</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>20.043</v>
+        <v>20.437</v>
       </c>
       <c r="D47">
-        <v>0.373</v>
+        <v>0.39</v>
       </c>
       <c r="E47">
-        <v>0.61</v>
+        <v>0.624</v>
       </c>
       <c r="F47">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G47">
-        <v>18.86</v>
+        <v>19.229</v>
       </c>
       <c r="H47">
-        <v>21.253</v>
+        <v>21.675</v>
       </c>
       <c r="I47">
-        <v>18.808</v>
+        <v>19.188</v>
       </c>
       <c r="J47">
-        <v>21.233</v>
+        <v>21.673</v>
       </c>
       <c r="K47">
-        <v>18.866</v>
+        <v>19.217</v>
       </c>
       <c r="L47">
-        <v>21.291</v>
+        <v>21.701</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>19.88</v>
+        <v>20.105</v>
       </c>
       <c r="D48">
-        <v>0.436</v>
+        <v>0.441</v>
       </c>
       <c r="E48">
-        <v>0.66</v>
+        <v>0.664</v>
       </c>
       <c r="F48">
         <v>0.021</v>
       </c>
       <c r="G48">
-        <v>18.537</v>
+        <v>18.752</v>
       </c>
       <c r="H48">
-        <v>21.124</v>
+        <v>21.355</v>
       </c>
       <c r="I48">
-        <v>18.573</v>
+        <v>18.755</v>
       </c>
       <c r="J48">
-        <v>21.165</v>
+        <v>21.365</v>
       </c>
       <c r="K48">
-        <v>18.545</v>
+        <v>18.793</v>
       </c>
       <c r="L48">
-        <v>21.138</v>
+        <v>21.403</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>18.081</v>
+        <v>18.376</v>
       </c>
       <c r="D49">
-        <v>0.332</v>
+        <v>0.351</v>
       </c>
       <c r="E49">
-        <v>0.576</v>
+        <v>0.593</v>
       </c>
       <c r="F49">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="G49">
-        <v>16.945</v>
+        <v>17.205</v>
       </c>
       <c r="H49">
-        <v>19.203</v>
+        <v>19.529</v>
       </c>
       <c r="I49">
-        <v>16.993</v>
+        <v>17.228</v>
       </c>
       <c r="J49">
-        <v>19.174</v>
+        <v>19.499</v>
       </c>
       <c r="K49">
-        <v>16.98</v>
+        <v>17.244</v>
       </c>
       <c r="L49">
-        <v>19.161</v>
+        <v>19.514</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>245.632</v>
+        <v>230.274</v>
       </c>
       <c r="D2">
-        <v>5.731</v>
+        <v>4.694</v>
       </c>
       <c r="E2">
-        <v>2.394</v>
+        <v>2.167</v>
       </c>
       <c r="F2">
-        <v>0.076</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G2">
-        <v>241.003</v>
+        <v>226.118</v>
       </c>
       <c r="H2">
-        <v>250.387</v>
+        <v>234.611</v>
       </c>
       <c r="I2">
-        <v>241.079</v>
+        <v>226.075</v>
       </c>
       <c r="J2">
-        <v>250.037</v>
+        <v>234.401</v>
       </c>
       <c r="K2">
-        <v>241.29</v>
+        <v>226.238</v>
       </c>
       <c r="L2">
-        <v>250.249</v>
+        <v>234.564</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>165.399</v>
+        <v>163.843</v>
       </c>
       <c r="D3">
-        <v>3.152</v>
+        <v>2.956</v>
       </c>
       <c r="E3">
-        <v>1.775</v>
+        <v>1.719</v>
       </c>
       <c r="F3">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="G3">
-        <v>161.842</v>
+        <v>160.433</v>
       </c>
       <c r="H3">
-        <v>168.802</v>
+        <v>167.173</v>
       </c>
       <c r="I3">
-        <v>161.558</v>
+        <v>160.422</v>
       </c>
       <c r="J3">
-        <v>168.681</v>
+        <v>166.951</v>
       </c>
       <c r="K3">
-        <v>162.04</v>
+        <v>160.695</v>
       </c>
       <c r="L3">
-        <v>169.163</v>
+        <v>167.225</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>110.272</v>
+        <v>113.646</v>
       </c>
       <c r="D4">
-        <v>2.347</v>
+        <v>2.197</v>
       </c>
       <c r="E4">
-        <v>1.532</v>
+        <v>1.482</v>
       </c>
       <c r="F4">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="G4">
-        <v>107.183</v>
+        <v>110.635</v>
       </c>
       <c r="H4">
-        <v>113.188</v>
+        <v>116.446</v>
       </c>
       <c r="I4">
-        <v>107.217</v>
+        <v>110.702</v>
       </c>
       <c r="J4">
-        <v>113.099</v>
+        <v>116.47</v>
       </c>
       <c r="K4">
-        <v>107.358</v>
+        <v>110.716</v>
       </c>
       <c r="L4">
-        <v>113.24</v>
+        <v>116.485</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>78.464</v>
+        <v>80.816</v>
       </c>
       <c r="D5">
-        <v>2.548</v>
+        <v>2.506</v>
       </c>
       <c r="E5">
-        <v>1.596</v>
+        <v>1.583</v>
       </c>
       <c r="F5">
         <v>0.05</v>
       </c>
       <c r="G5">
-        <v>75.188</v>
+        <v>77.574</v>
       </c>
       <c r="H5">
-        <v>81.446</v>
+        <v>83.779</v>
       </c>
       <c r="I5">
-        <v>75.01300000000001</v>
+        <v>77.29300000000001</v>
       </c>
       <c r="J5">
-        <v>81.28</v>
+        <v>83.663</v>
       </c>
       <c r="K5">
-        <v>75.5</v>
+        <v>77.82899999999999</v>
       </c>
       <c r="L5">
-        <v>81.767</v>
+        <v>84.199</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>60.469</v>
+        <v>61.81</v>
       </c>
       <c r="D6">
-        <v>1.028</v>
+        <v>1.035</v>
       </c>
       <c r="E6">
-        <v>1.014</v>
+        <v>1.017</v>
       </c>
       <c r="F6">
         <v>0.032</v>
       </c>
       <c r="G6">
-        <v>58.548</v>
+        <v>59.858</v>
       </c>
       <c r="H6">
-        <v>62.523</v>
+        <v>63.846</v>
       </c>
       <c r="I6">
-        <v>58.55</v>
+        <v>59.866</v>
       </c>
       <c r="J6">
-        <v>62.578</v>
+        <v>63.838</v>
       </c>
       <c r="K6">
-        <v>58.427</v>
+        <v>59.825</v>
       </c>
       <c r="L6">
-        <v>62.455</v>
+        <v>63.797</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>49.306</v>
+        <v>49.495</v>
       </c>
       <c r="D7">
-        <v>0.946</v>
+        <v>0.852</v>
       </c>
       <c r="E7">
-        <v>0.973</v>
+        <v>0.923</v>
       </c>
       <c r="F7">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="G7">
-        <v>47.421</v>
+        <v>47.686</v>
       </c>
       <c r="H7">
-        <v>51.234</v>
+        <v>51.305</v>
       </c>
       <c r="I7">
-        <v>47.381</v>
+        <v>47.709</v>
       </c>
       <c r="J7">
-        <v>51.166</v>
+        <v>51.198</v>
       </c>
       <c r="K7">
-        <v>47.467</v>
+        <v>47.792</v>
       </c>
       <c r="L7">
-        <v>51.251</v>
+        <v>51.281</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>42.718</v>
+        <v>41.72</v>
       </c>
       <c r="D8">
-        <v>0.887</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E8">
-        <v>0.9419999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="F8">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="G8">
-        <v>40.93</v>
+        <v>40.121</v>
       </c>
       <c r="H8">
-        <v>44.623</v>
+        <v>43.375</v>
       </c>
       <c r="I8">
-        <v>40.686</v>
+        <v>39.984</v>
       </c>
       <c r="J8">
-        <v>44.58</v>
+        <v>43.367</v>
       </c>
       <c r="K8">
-        <v>40.915</v>
+        <v>40.101</v>
       </c>
       <c r="L8">
-        <v>44.809</v>
+        <v>43.484</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>37.092</v>
+        <v>36.093</v>
       </c>
       <c r="D9">
-        <v>0.776</v>
+        <v>0.62</v>
       </c>
       <c r="E9">
-        <v>0.881</v>
+        <v>0.787</v>
       </c>
       <c r="F9">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="G9">
-        <v>35.344</v>
+        <v>34.518</v>
       </c>
       <c r="H9">
-        <v>38.796</v>
+        <v>37.605</v>
       </c>
       <c r="I9">
-        <v>35.305</v>
+        <v>34.501</v>
       </c>
       <c r="J9">
-        <v>38.735</v>
+        <v>37.609</v>
       </c>
       <c r="K9">
-        <v>35.427</v>
+        <v>34.545</v>
       </c>
       <c r="L9">
-        <v>38.857</v>
+        <v>37.653</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>33.086</v>
+        <v>31.906</v>
       </c>
       <c r="D10">
-        <v>0.643</v>
+        <v>0.515</v>
       </c>
       <c r="E10">
-        <v>0.802</v>
+        <v>0.717</v>
       </c>
       <c r="F10">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="G10">
-        <v>31.505</v>
+        <v>30.493</v>
       </c>
       <c r="H10">
-        <v>34.647</v>
+        <v>33.304</v>
       </c>
       <c r="I10">
-        <v>31.495</v>
+        <v>30.457</v>
       </c>
       <c r="J10">
-        <v>34.625</v>
+        <v>33.273</v>
       </c>
       <c r="K10">
-        <v>31.538</v>
+        <v>30.531</v>
       </c>
       <c r="L10">
-        <v>34.667</v>
+        <v>33.347</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>31.907</v>
+        <v>30.717</v>
       </c>
       <c r="D11">
-        <v>0.575</v>
+        <v>0.47</v>
       </c>
       <c r="E11">
-        <v>0.758</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F11">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="G11">
-        <v>30.399</v>
+        <v>29.361</v>
       </c>
       <c r="H11">
-        <v>33.37</v>
+        <v>32.048</v>
       </c>
       <c r="I11">
-        <v>30.341</v>
+        <v>29.308</v>
       </c>
       <c r="J11">
-        <v>33.309</v>
+        <v>32.022</v>
       </c>
       <c r="K11">
-        <v>30.482</v>
+        <v>29.399</v>
       </c>
       <c r="L11">
-        <v>33.45</v>
+        <v>32.113</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>29.861</v>
+        <v>28.684</v>
       </c>
       <c r="D12">
-        <v>0.639</v>
+        <v>0.574</v>
       </c>
       <c r="E12">
-        <v>0.799</v>
+        <v>0.758</v>
       </c>
       <c r="F12">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="G12">
-        <v>28.206</v>
+        <v>27.122</v>
       </c>
       <c r="H12">
-        <v>31.339</v>
+        <v>30.092</v>
       </c>
       <c r="I12">
-        <v>28.157</v>
+        <v>27.069</v>
       </c>
       <c r="J12">
-        <v>31.26</v>
+        <v>30.071</v>
       </c>
       <c r="K12">
-        <v>28.373</v>
+        <v>27.22</v>
       </c>
       <c r="L12">
-        <v>31.476</v>
+        <v>30.221</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>30.567</v>
+        <v>29.37</v>
       </c>
       <c r="D13">
-        <v>0.575</v>
+        <v>0.512</v>
       </c>
       <c r="E13">
-        <v>0.758</v>
+        <v>0.715</v>
       </c>
       <c r="F13">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="G13">
-        <v>29.044</v>
+        <v>27.929</v>
       </c>
       <c r="H13">
-        <v>32.015</v>
+        <v>30.733</v>
       </c>
       <c r="I13">
-        <v>29.003</v>
+        <v>27.844</v>
       </c>
       <c r="J13">
-        <v>31.988</v>
+        <v>30.729</v>
       </c>
       <c r="K13">
-        <v>29.109</v>
+        <v>27.972</v>
       </c>
       <c r="L13">
-        <v>32.094</v>
+        <v>30.857</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>26.179</v>
+        <v>25.117</v>
       </c>
       <c r="D14">
-        <v>0.454</v>
+        <v>0.365</v>
       </c>
       <c r="E14">
-        <v>0.674</v>
+        <v>0.604</v>
       </c>
       <c r="F14">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="G14">
-        <v>24.856</v>
+        <v>23.926</v>
       </c>
       <c r="H14">
-        <v>27.497</v>
+        <v>26.294</v>
       </c>
       <c r="I14">
-        <v>24.85</v>
+        <v>23.879</v>
       </c>
       <c r="J14">
-        <v>27.451</v>
+        <v>26.263</v>
       </c>
       <c r="K14">
-        <v>24.904</v>
+        <v>23.964</v>
       </c>
       <c r="L14">
-        <v>27.504</v>
+        <v>26.348</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>26.297</v>
+        <v>25.12</v>
       </c>
       <c r="D15">
-        <v>0.473</v>
+        <v>0.395</v>
       </c>
       <c r="E15">
-        <v>0.6879999999999999</v>
+        <v>0.629</v>
       </c>
       <c r="F15">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="G15">
-        <v>24.971</v>
+        <v>23.895</v>
       </c>
       <c r="H15">
-        <v>27.667</v>
+        <v>26.359</v>
       </c>
       <c r="I15">
-        <v>24.985</v>
+        <v>23.919</v>
       </c>
       <c r="J15">
-        <v>27.655</v>
+        <v>26.346</v>
       </c>
       <c r="K15">
-        <v>24.961</v>
+        <v>23.901</v>
       </c>
       <c r="L15">
-        <v>27.631</v>
+        <v>26.328</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>24.677</v>
+        <v>23.611</v>
       </c>
       <c r="D16">
-        <v>0.525</v>
+        <v>0.401</v>
       </c>
       <c r="E16">
-        <v>0.724</v>
+        <v>0.633</v>
       </c>
       <c r="F16">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="G16">
-        <v>23.206</v>
+        <v>22.313</v>
       </c>
       <c r="H16">
-        <v>26.046</v>
+        <v>24.794</v>
       </c>
       <c r="I16">
-        <v>23.157</v>
+        <v>22.264</v>
       </c>
       <c r="J16">
-        <v>26.03</v>
+        <v>24.77</v>
       </c>
       <c r="K16">
-        <v>23.272</v>
+        <v>22.395</v>
       </c>
       <c r="L16">
-        <v>26.146</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>24.241</v>
+        <v>23.72</v>
       </c>
       <c r="D17">
-        <v>0.445</v>
+        <v>0.437</v>
       </c>
       <c r="E17">
-        <v>0.667</v>
+        <v>0.661</v>
       </c>
       <c r="F17">
         <v>0.021</v>
       </c>
       <c r="G17">
-        <v>22.894</v>
+        <v>22.381</v>
       </c>
       <c r="H17">
-        <v>25.509</v>
+        <v>24.972</v>
       </c>
       <c r="I17">
-        <v>22.909</v>
+        <v>22.351</v>
       </c>
       <c r="J17">
-        <v>25.492</v>
+        <v>24.958</v>
       </c>
       <c r="K17">
-        <v>22.95</v>
+        <v>22.438</v>
       </c>
       <c r="L17">
-        <v>25.534</v>
+        <v>25.046</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>24.012</v>
+        <v>22.948</v>
       </c>
       <c r="D18">
-        <v>0.476</v>
+        <v>0.406</v>
       </c>
       <c r="E18">
-        <v>0.6899999999999999</v>
+        <v>0.637</v>
       </c>
       <c r="F18">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="G18">
-        <v>22.645</v>
+        <v>21.682</v>
       </c>
       <c r="H18">
-        <v>25.349</v>
+        <v>24.178</v>
       </c>
       <c r="I18">
-        <v>22.618</v>
+        <v>21.596</v>
       </c>
       <c r="J18">
-        <v>25.291</v>
+        <v>24.141</v>
       </c>
       <c r="K18">
-        <v>22.718</v>
+        <v>21.737</v>
       </c>
       <c r="L18">
-        <v>25.391</v>
+        <v>24.281</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>22.046</v>
+        <v>21.272</v>
       </c>
       <c r="D19">
-        <v>0.412</v>
+        <v>0.377</v>
       </c>
       <c r="E19">
-        <v>0.642</v>
+        <v>0.614</v>
       </c>
       <c r="F19">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="G19">
-        <v>20.744</v>
+        <v>20.011</v>
       </c>
       <c r="H19">
-        <v>23.259</v>
+        <v>22.416</v>
       </c>
       <c r="I19">
-        <v>20.729</v>
+        <v>19.983</v>
       </c>
       <c r="J19">
-        <v>23.226</v>
+        <v>22.42</v>
       </c>
       <c r="K19">
-        <v>20.821</v>
+        <v>20.065</v>
       </c>
       <c r="L19">
-        <v>23.318</v>
+        <v>22.502</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>21.673</v>
+        <v>20.571</v>
       </c>
       <c r="D20">
-        <v>0.741</v>
+        <v>0.339</v>
       </c>
       <c r="E20">
-        <v>0.861</v>
+        <v>0.582</v>
       </c>
       <c r="F20">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="G20">
-        <v>19.974</v>
+        <v>19.415</v>
       </c>
       <c r="H20">
-        <v>23.348</v>
+        <v>21.696</v>
       </c>
       <c r="I20">
-        <v>19.698</v>
+        <v>19.316</v>
       </c>
       <c r="J20">
-        <v>23.205</v>
+        <v>21.684</v>
       </c>
       <c r="K20">
-        <v>20.129</v>
+        <v>19.443</v>
       </c>
       <c r="L20">
-        <v>23.635</v>
+        <v>21.811</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>20.777</v>
+        <v>19.884</v>
       </c>
       <c r="D21">
-        <v>0.408</v>
+        <v>0.338</v>
       </c>
       <c r="E21">
-        <v>0.639</v>
+        <v>0.582</v>
       </c>
       <c r="F21">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="G21">
-        <v>19.461</v>
+        <v>18.681</v>
       </c>
       <c r="H21">
-        <v>21.965</v>
+        <v>20.961</v>
       </c>
       <c r="I21">
-        <v>19.423</v>
+        <v>18.6</v>
       </c>
       <c r="J21">
-        <v>21.953</v>
+        <v>20.963</v>
       </c>
       <c r="K21">
-        <v>19.537</v>
+        <v>18.742</v>
       </c>
       <c r="L21">
-        <v>22.067</v>
+        <v>21.105</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>19.881</v>
+        <v>19.223</v>
       </c>
       <c r="D22">
-        <v>0.435</v>
+        <v>0.368</v>
       </c>
       <c r="E22">
-        <v>0.66</v>
+        <v>0.606</v>
       </c>
       <c r="F22">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="G22">
-        <v>18.612</v>
+        <v>18.044</v>
       </c>
       <c r="H22">
-        <v>21.198</v>
+        <v>20.42</v>
       </c>
       <c r="I22">
-        <v>18.583</v>
+        <v>18.06</v>
       </c>
       <c r="J22">
-        <v>21.156</v>
+        <v>20.369</v>
       </c>
       <c r="K22">
-        <v>18.631</v>
+        <v>18.085</v>
       </c>
       <c r="L22">
-        <v>21.204</v>
+        <v>20.395</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>18.293</v>
+        <v>17.65</v>
       </c>
       <c r="D23">
-        <v>0.32</v>
+        <v>0.296</v>
       </c>
       <c r="E23">
-        <v>0.5649999999999999</v>
+        <v>0.544</v>
       </c>
       <c r="F23">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G23">
-        <v>17.224</v>
+        <v>16.611</v>
       </c>
       <c r="H23">
-        <v>19.441</v>
+        <v>18.745</v>
       </c>
       <c r="I23">
-        <v>17.196</v>
+        <v>16.595</v>
       </c>
       <c r="J23">
-        <v>19.445</v>
+        <v>18.777</v>
       </c>
       <c r="K23">
-        <v>17.18</v>
+        <v>16.55</v>
       </c>
       <c r="L23">
-        <v>19.43</v>
+        <v>18.732</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>17.985</v>
+        <v>17.5</v>
       </c>
       <c r="D24">
-        <v>0.375</v>
+        <v>0.35</v>
       </c>
       <c r="E24">
-        <v>0.612</v>
+        <v>0.591</v>
       </c>
       <c r="F24">
         <v>0.019</v>
       </c>
       <c r="G24">
-        <v>16.786</v>
+        <v>16.33</v>
       </c>
       <c r="H24">
-        <v>19.186</v>
+        <v>18.649</v>
       </c>
       <c r="I24">
-        <v>16.789</v>
+        <v>16.333</v>
       </c>
       <c r="J24">
-        <v>19.192</v>
+        <v>18.704</v>
       </c>
       <c r="K24">
-        <v>16.779</v>
+        <v>16.286</v>
       </c>
       <c r="L24">
-        <v>19.181</v>
+        <v>18.657</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>16.462</v>
+        <v>16.141</v>
       </c>
       <c r="D25">
-        <v>0.271</v>
+        <v>0.259</v>
       </c>
       <c r="E25">
-        <v>0.52</v>
+        <v>0.509</v>
       </c>
       <c r="F25">
         <v>0.016</v>
       </c>
       <c r="G25">
-        <v>15.43</v>
+        <v>15.139</v>
       </c>
       <c r="H25">
-        <v>17.468</v>
+        <v>17.136</v>
       </c>
       <c r="I25">
-        <v>15.345</v>
+        <v>15.065</v>
       </c>
       <c r="J25">
-        <v>17.413</v>
+        <v>17.08</v>
       </c>
       <c r="K25">
-        <v>15.498</v>
+        <v>15.199</v>
       </c>
       <c r="L25">
-        <v>17.566</v>
+        <v>17.214</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>274.236</v>
+        <v>257.074</v>
       </c>
       <c r="D26">
-        <v>6.982</v>
+        <v>5.839</v>
       </c>
       <c r="E26">
-        <v>2.642</v>
+        <v>2.416</v>
       </c>
       <c r="F26">
-        <v>0.08400000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="G26">
-        <v>269.113</v>
+        <v>252.456</v>
       </c>
       <c r="H26">
-        <v>279.47</v>
+        <v>261.928</v>
       </c>
       <c r="I26">
-        <v>269.102</v>
+        <v>252.289</v>
       </c>
       <c r="J26">
-        <v>279.38</v>
+        <v>261.758</v>
       </c>
       <c r="K26">
-        <v>269.147</v>
+        <v>252.508</v>
       </c>
       <c r="L26">
-        <v>279.426</v>
+        <v>261.977</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>184.595</v>
+        <v>182.884</v>
       </c>
       <c r="D27">
-        <v>4.237</v>
+        <v>3.958</v>
       </c>
       <c r="E27">
-        <v>2.058</v>
+        <v>1.989</v>
       </c>
       <c r="F27">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="G27">
-        <v>180.594</v>
+        <v>179.008</v>
       </c>
       <c r="H27">
-        <v>188.663</v>
+        <v>186.807</v>
       </c>
       <c r="I27">
-        <v>180.308</v>
+        <v>178.862</v>
       </c>
       <c r="J27">
-        <v>188.566</v>
+        <v>186.655</v>
       </c>
       <c r="K27">
-        <v>180.657</v>
+        <v>179.136</v>
       </c>
       <c r="L27">
-        <v>188.915</v>
+        <v>186.929</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>123.027</v>
+        <v>126.795</v>
       </c>
       <c r="D28">
-        <v>2.885</v>
+        <v>2.631</v>
       </c>
       <c r="E28">
-        <v>1.699</v>
+        <v>1.622</v>
       </c>
       <c r="F28">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="G28">
-        <v>119.766</v>
+        <v>123.661</v>
       </c>
       <c r="H28">
-        <v>126.425</v>
+        <v>130.019</v>
       </c>
       <c r="I28">
-        <v>119.354</v>
+        <v>123.529</v>
       </c>
       <c r="J28">
-        <v>126.323</v>
+        <v>129.943</v>
       </c>
       <c r="K28">
-        <v>119.8</v>
+        <v>123.692</v>
       </c>
       <c r="L28">
-        <v>126.768</v>
+        <v>130.107</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>87.504</v>
+        <v>90.12</v>
       </c>
       <c r="D29">
-        <v>3.291</v>
+        <v>3.175</v>
       </c>
       <c r="E29">
-        <v>1.814</v>
+        <v>1.782</v>
       </c>
       <c r="F29">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="G29">
-        <v>83.974</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="H29">
-        <v>91.08499999999999</v>
+        <v>93.666</v>
       </c>
       <c r="I29">
-        <v>83.506</v>
+        <v>86.289</v>
       </c>
       <c r="J29">
-        <v>90.822</v>
+        <v>93.38800000000001</v>
       </c>
       <c r="K29">
-        <v>84.211</v>
+        <v>86.90600000000001</v>
       </c>
       <c r="L29">
-        <v>91.527</v>
+        <v>94.005</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>67.52</v>
+        <v>69.002</v>
       </c>
       <c r="D30">
-        <v>1.344</v>
+        <v>1.329</v>
       </c>
       <c r="E30">
-        <v>1.159</v>
+        <v>1.153</v>
       </c>
       <c r="F30">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="G30">
-        <v>65.3</v>
+        <v>66.798</v>
       </c>
       <c r="H30">
-        <v>69.84399999999999</v>
+        <v>71.31699999999999</v>
       </c>
       <c r="I30">
-        <v>65.205</v>
+        <v>66.703</v>
       </c>
       <c r="J30">
-        <v>69.873</v>
+        <v>71.247</v>
       </c>
       <c r="K30">
-        <v>65.21899999999999</v>
+        <v>66.812</v>
       </c>
       <c r="L30">
-        <v>69.887</v>
+        <v>71.35599999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>55.079</v>
+        <v>55.284</v>
       </c>
       <c r="D31">
-        <v>1.146</v>
+        <v>1.065</v>
       </c>
       <c r="E31">
-        <v>1.07</v>
+        <v>1.032</v>
       </c>
       <c r="F31">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="G31">
-        <v>52.938</v>
+        <v>53.209</v>
       </c>
       <c r="H31">
-        <v>57.135</v>
+        <v>57.254</v>
       </c>
       <c r="I31">
-        <v>52.913</v>
+        <v>53.149</v>
       </c>
       <c r="J31">
-        <v>57.052</v>
+        <v>57.223</v>
       </c>
       <c r="K31">
-        <v>53.063</v>
+        <v>53.292</v>
       </c>
       <c r="L31">
-        <v>57.202</v>
+        <v>57.366</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>47.727</v>
+        <v>46.587</v>
       </c>
       <c r="D32">
-        <v>1.16</v>
+        <v>0.907</v>
       </c>
       <c r="E32">
-        <v>1.077</v>
+        <v>0.952</v>
       </c>
       <c r="F32">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="G32">
-        <v>45.611</v>
+        <v>44.732</v>
       </c>
       <c r="H32">
-        <v>49.832</v>
+        <v>48.466</v>
       </c>
       <c r="I32">
-        <v>45.522</v>
+        <v>44.667</v>
       </c>
       <c r="J32">
-        <v>49.878</v>
+        <v>48.457</v>
       </c>
       <c r="K32">
-        <v>45.57</v>
+        <v>44.729</v>
       </c>
       <c r="L32">
-        <v>49.926</v>
+        <v>48.518</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>41.435</v>
+        <v>40.314</v>
       </c>
       <c r="D33">
-        <v>0.9360000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="E33">
-        <v>0.967</v>
+        <v>0.871</v>
       </c>
       <c r="F33">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="G33">
-        <v>39.464</v>
+        <v>38.532</v>
       </c>
       <c r="H33">
-        <v>43.256</v>
+        <v>41.948</v>
       </c>
       <c r="I33">
-        <v>39.498</v>
+        <v>38.577</v>
       </c>
       <c r="J33">
-        <v>43.333</v>
+        <v>42.03</v>
       </c>
       <c r="K33">
-        <v>39.463</v>
+        <v>38.525</v>
       </c>
       <c r="L33">
-        <v>43.298</v>
+        <v>41.977</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>36.966</v>
+        <v>35.655</v>
       </c>
       <c r="D34">
-        <v>0.713</v>
+        <v>0.586</v>
       </c>
       <c r="E34">
-        <v>0.844</v>
+        <v>0.765</v>
       </c>
       <c r="F34">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="G34">
-        <v>35.245</v>
+        <v>34.077</v>
       </c>
       <c r="H34">
-        <v>38.555</v>
+        <v>37.077</v>
       </c>
       <c r="I34">
-        <v>35.258</v>
+        <v>34.023</v>
       </c>
       <c r="J34">
-        <v>38.573</v>
+        <v>37.077</v>
       </c>
       <c r="K34">
-        <v>35.292</v>
+        <v>34.156</v>
       </c>
       <c r="L34">
-        <v>38.607</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>35.628</v>
+        <v>34.306</v>
       </c>
       <c r="D35">
-        <v>0.6879999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E35">
-        <v>0.829</v>
+        <v>0.753</v>
       </c>
       <c r="F35">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="G35">
-        <v>33.965</v>
+        <v>32.789</v>
       </c>
       <c r="H35">
-        <v>37.215</v>
+        <v>35.742</v>
       </c>
       <c r="I35">
-        <v>33.881</v>
+        <v>32.705</v>
       </c>
       <c r="J35">
-        <v>37.246</v>
+        <v>35.782</v>
       </c>
       <c r="K35">
-        <v>33.972</v>
+        <v>32.79</v>
       </c>
       <c r="L35">
-        <v>37.336</v>
+        <v>35.867</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>33.254</v>
+        <v>31.949</v>
       </c>
       <c r="D36">
-        <v>0.721</v>
+        <v>0.644</v>
       </c>
       <c r="E36">
-        <v>0.849</v>
+        <v>0.802</v>
       </c>
       <c r="F36">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="G36">
-        <v>31.657</v>
+        <v>30.439</v>
       </c>
       <c r="H36">
-        <v>34.986</v>
+        <v>33.583</v>
       </c>
       <c r="I36">
-        <v>31.611</v>
+        <v>30.442</v>
       </c>
       <c r="J36">
-        <v>34.92</v>
+        <v>33.447</v>
       </c>
       <c r="K36">
-        <v>31.656</v>
+        <v>30.513</v>
       </c>
       <c r="L36">
-        <v>34.964</v>
+        <v>33.518</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>34.096</v>
+        <v>32.762</v>
       </c>
       <c r="D37">
-        <v>0.656</v>
+        <v>0.569</v>
       </c>
       <c r="E37">
-        <v>0.8100000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="F37">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="G37">
-        <v>32.526</v>
+        <v>31.295</v>
       </c>
       <c r="H37">
-        <v>35.701</v>
+        <v>34.252</v>
       </c>
       <c r="I37">
-        <v>32.479</v>
+        <v>31.313</v>
       </c>
       <c r="J37">
-        <v>35.64</v>
+        <v>34.205</v>
       </c>
       <c r="K37">
-        <v>32.57</v>
+        <v>31.33</v>
       </c>
       <c r="L37">
-        <v>35.731</v>
+        <v>34.222</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>29.246</v>
+        <v>28.061</v>
       </c>
       <c r="D38">
-        <v>0.535</v>
+        <v>0.446</v>
       </c>
       <c r="E38">
-        <v>0.732</v>
+        <v>0.668</v>
       </c>
       <c r="F38">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="G38">
-        <v>27.77</v>
+        <v>26.704</v>
       </c>
       <c r="H38">
-        <v>30.638</v>
+        <v>29.323</v>
       </c>
       <c r="I38">
-        <v>27.681</v>
+        <v>26.648</v>
       </c>
       <c r="J38">
-        <v>30.641</v>
+        <v>29.319</v>
       </c>
       <c r="K38">
-        <v>27.81</v>
+        <v>26.755</v>
       </c>
       <c r="L38">
-        <v>30.769</v>
+        <v>29.426</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>29.39</v>
+        <v>28.06</v>
       </c>
       <c r="D39">
-        <v>0.535</v>
+        <v>0.439</v>
       </c>
       <c r="E39">
-        <v>0.732</v>
+        <v>0.663</v>
       </c>
       <c r="F39">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="G39">
-        <v>27.918</v>
+        <v>26.738</v>
       </c>
       <c r="H39">
-        <v>30.786</v>
+        <v>29.336</v>
       </c>
       <c r="I39">
-        <v>27.819</v>
+        <v>26.755</v>
       </c>
       <c r="J39">
-        <v>30.805</v>
+        <v>29.343</v>
       </c>
       <c r="K39">
-        <v>27.936</v>
+        <v>26.754</v>
       </c>
       <c r="L39">
-        <v>30.922</v>
+        <v>29.342</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>27.527</v>
+        <v>26.325</v>
       </c>
       <c r="D40">
-        <v>0.576</v>
+        <v>0.445</v>
       </c>
       <c r="E40">
-        <v>0.759</v>
+        <v>0.667</v>
       </c>
       <c r="F40">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="G40">
-        <v>26.028</v>
+        <v>25.023</v>
       </c>
       <c r="H40">
-        <v>29.003</v>
+        <v>27.638</v>
       </c>
       <c r="I40">
-        <v>26.033</v>
+        <v>24.964</v>
       </c>
       <c r="J40">
-        <v>28.927</v>
+        <v>27.586</v>
       </c>
       <c r="K40">
-        <v>26.115</v>
+        <v>25.07</v>
       </c>
       <c r="L40">
-        <v>29.01</v>
+        <v>27.691</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>27.049</v>
+        <v>26.472</v>
       </c>
       <c r="D41">
-        <v>0.5679999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="E41">
-        <v>0.754</v>
+        <v>0.743</v>
       </c>
       <c r="F41">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="G41">
-        <v>25.556</v>
+        <v>24.986</v>
       </c>
       <c r="H41">
-        <v>28.511</v>
+        <v>27.899</v>
       </c>
       <c r="I41">
-        <v>25.563</v>
+        <v>24.974</v>
       </c>
       <c r="J41">
-        <v>28.438</v>
+        <v>27.802</v>
       </c>
       <c r="K41">
-        <v>25.645</v>
+        <v>25.113</v>
       </c>
       <c r="L41">
-        <v>28.52</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>26.811</v>
+        <v>25.621</v>
       </c>
       <c r="D42">
-        <v>0.577</v>
+        <v>0.495</v>
       </c>
       <c r="E42">
-        <v>0.759</v>
+        <v>0.703</v>
       </c>
       <c r="F42">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="G42">
-        <v>25.298</v>
+        <v>24.219</v>
       </c>
       <c r="H42">
-        <v>28.275</v>
+        <v>26.976</v>
       </c>
       <c r="I42">
-        <v>25.248</v>
+        <v>24.181</v>
       </c>
       <c r="J42">
-        <v>28.227</v>
+        <v>26.95</v>
       </c>
       <c r="K42">
-        <v>25.371</v>
+        <v>24.268</v>
       </c>
       <c r="L42">
-        <v>28.35</v>
+        <v>27.038</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>24.561</v>
+        <v>23.696</v>
       </c>
       <c r="D43">
-        <v>0.501</v>
+        <v>0.448</v>
       </c>
       <c r="E43">
-        <v>0.708</v>
+        <v>0.669</v>
       </c>
       <c r="F43">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="G43">
-        <v>23.227</v>
+        <v>22.424</v>
       </c>
       <c r="H43">
-        <v>26.001</v>
+        <v>25.048</v>
       </c>
       <c r="I43">
-        <v>23.128</v>
+        <v>22.308</v>
       </c>
       <c r="J43">
-        <v>25.96</v>
+        <v>24.973</v>
       </c>
       <c r="K43">
-        <v>23.215</v>
+        <v>22.459</v>
       </c>
       <c r="L43">
-        <v>26.047</v>
+        <v>25.124</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>24.162</v>
+        <v>22.951</v>
       </c>
       <c r="D44">
-        <v>0.978</v>
+        <v>0.45</v>
       </c>
       <c r="E44">
-        <v>0.989</v>
+        <v>0.671</v>
       </c>
       <c r="F44">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="G44">
-        <v>22.278</v>
+        <v>21.649</v>
       </c>
       <c r="H44">
-        <v>26.155</v>
+        <v>24.278</v>
       </c>
       <c r="I44">
-        <v>21.913</v>
+        <v>21.644</v>
       </c>
       <c r="J44">
-        <v>25.914</v>
+        <v>24.231</v>
       </c>
       <c r="K44">
-        <v>22.465</v>
+        <v>21.684</v>
       </c>
       <c r="L44">
-        <v>26.465</v>
+        <v>24.271</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>23.186</v>
+        <v>22.178</v>
       </c>
       <c r="D45">
-        <v>0.488</v>
+        <v>0.404</v>
       </c>
       <c r="E45">
-        <v>0.699</v>
+        <v>0.636</v>
       </c>
       <c r="F45">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="G45">
-        <v>21.765</v>
+        <v>20.903</v>
       </c>
       <c r="H45">
-        <v>24.504</v>
+        <v>23.396</v>
       </c>
       <c r="I45">
-        <v>21.715</v>
+        <v>20.858</v>
       </c>
       <c r="J45">
-        <v>24.451</v>
+        <v>23.355</v>
       </c>
       <c r="K45">
-        <v>21.869</v>
+        <v>20.973</v>
       </c>
       <c r="L45">
-        <v>24.605</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>22.221</v>
+        <v>21.467</v>
       </c>
       <c r="D46">
-        <v>0.504</v>
+        <v>0.427</v>
       </c>
       <c r="E46">
-        <v>0.71</v>
+        <v>0.653</v>
       </c>
       <c r="F46">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="G46">
-        <v>20.806</v>
+        <v>20.185</v>
       </c>
       <c r="H46">
-        <v>23.589</v>
+        <v>22.745</v>
       </c>
       <c r="I46">
-        <v>20.733</v>
+        <v>20.091</v>
       </c>
       <c r="J46">
-        <v>23.552</v>
+        <v>22.752</v>
       </c>
       <c r="K46">
-        <v>20.867</v>
+        <v>20.18</v>
       </c>
       <c r="L46">
-        <v>23.685</v>
+        <v>22.841</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>20.437</v>
+        <v>19.707</v>
       </c>
       <c r="D47">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="E47">
-        <v>0.624</v>
+        <v>0.6</v>
       </c>
       <c r="F47">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="G47">
-        <v>19.229</v>
+        <v>18.557</v>
       </c>
       <c r="H47">
-        <v>21.675</v>
+        <v>20.91</v>
       </c>
       <c r="I47">
-        <v>19.188</v>
+        <v>18.512</v>
       </c>
       <c r="J47">
-        <v>21.673</v>
+        <v>20.886</v>
       </c>
       <c r="K47">
-        <v>19.217</v>
+        <v>18.555</v>
       </c>
       <c r="L47">
-        <v>21.701</v>
+        <v>20.929</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>20.105</v>
+        <v>19.552</v>
       </c>
       <c r="D48">
-        <v>0.441</v>
+        <v>0.414</v>
       </c>
       <c r="E48">
-        <v>0.664</v>
+        <v>0.643</v>
       </c>
       <c r="F48">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="G48">
-        <v>18.752</v>
+        <v>18.251</v>
       </c>
       <c r="H48">
-        <v>21.355</v>
+        <v>20.772</v>
       </c>
       <c r="I48">
-        <v>18.755</v>
+        <v>18.227</v>
       </c>
       <c r="J48">
-        <v>21.365</v>
+        <v>20.757</v>
       </c>
       <c r="K48">
-        <v>18.793</v>
+        <v>18.306</v>
       </c>
       <c r="L48">
-        <v>21.403</v>
+        <v>20.836</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>18.376</v>
+        <v>18.022</v>
       </c>
       <c r="D49">
-        <v>0.351</v>
+        <v>0.331</v>
       </c>
       <c r="E49">
-        <v>0.593</v>
+        <v>0.576</v>
       </c>
       <c r="F49">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="G49">
-        <v>17.205</v>
+        <v>16.887</v>
       </c>
       <c r="H49">
-        <v>19.529</v>
+        <v>19.143</v>
       </c>
       <c r="I49">
-        <v>17.228</v>
+        <v>16.935</v>
       </c>
       <c r="J49">
-        <v>19.499</v>
+        <v>19.099</v>
       </c>
       <c r="K49">
-        <v>17.244</v>
+        <v>16.938</v>
       </c>
       <c r="L49">
-        <v>19.514</v>
+        <v>19.102</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Monthly/monthly_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>230.274</v>
+        <v>245.916</v>
       </c>
       <c r="D2">
-        <v>4.694</v>
+        <v>5.473</v>
       </c>
       <c r="E2">
-        <v>2.167</v>
+        <v>2.339</v>
       </c>
       <c r="F2">
-        <v>0.06900000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="G2">
-        <v>226.118</v>
+        <v>241.404</v>
       </c>
       <c r="H2">
-        <v>234.611</v>
+        <v>250.574</v>
       </c>
       <c r="I2">
-        <v>226.075</v>
+        <v>241.43</v>
       </c>
       <c r="J2">
-        <v>234.401</v>
+        <v>250.251</v>
       </c>
       <c r="K2">
-        <v>226.238</v>
+        <v>241.654</v>
       </c>
       <c r="L2">
-        <v>234.564</v>
+        <v>250.475</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>163.843</v>
+        <v>166.09</v>
       </c>
       <c r="D3">
-        <v>2.956</v>
+        <v>3.103</v>
       </c>
       <c r="E3">
-        <v>1.719</v>
+        <v>1.761</v>
       </c>
       <c r="F3">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="G3">
-        <v>160.433</v>
+        <v>162.576</v>
       </c>
       <c r="H3">
-        <v>167.173</v>
+        <v>169.48</v>
       </c>
       <c r="I3">
-        <v>160.422</v>
+        <v>162.278</v>
       </c>
       <c r="J3">
-        <v>166.951</v>
+        <v>169.338</v>
       </c>
       <c r="K3">
-        <v>160.695</v>
+        <v>162.78</v>
       </c>
       <c r="L3">
-        <v>167.225</v>
+        <v>169.84</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>113.646</v>
+        <v>111.179</v>
       </c>
       <c r="D4">
-        <v>2.197</v>
+        <v>2.295</v>
       </c>
       <c r="E4">
-        <v>1.482</v>
+        <v>1.515</v>
       </c>
       <c r="F4">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="G4">
-        <v>110.635</v>
+        <v>108.113</v>
       </c>
       <c r="H4">
-        <v>116.446</v>
+        <v>114.051</v>
       </c>
       <c r="I4">
-        <v>110.702</v>
+        <v>108.155</v>
       </c>
       <c r="J4">
-        <v>116.47</v>
+        <v>114.033</v>
       </c>
       <c r="K4">
-        <v>110.716</v>
+        <v>108.228</v>
       </c>
       <c r="L4">
-        <v>116.485</v>
+        <v>114.106</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>80.816</v>
+        <v>79.096</v>
       </c>
       <c r="D5">
-        <v>2.506</v>
+        <v>2.563</v>
       </c>
       <c r="E5">
-        <v>1.583</v>
+        <v>1.601</v>
       </c>
       <c r="F5">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="G5">
-        <v>77.574</v>
+        <v>75.809</v>
       </c>
       <c r="H5">
-        <v>83.779</v>
+        <v>82.084</v>
       </c>
       <c r="I5">
-        <v>77.29300000000001</v>
+        <v>75.584</v>
       </c>
       <c r="J5">
-        <v>83.663</v>
+        <v>81.947</v>
       </c>
       <c r="K5">
-        <v>77.82899999999999</v>
+        <v>76.095</v>
       </c>
       <c r="L5">
-        <v>84.199</v>
+        <v>82.458</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>61.81</v>
+        <v>60.925</v>
       </c>
       <c r="D6">
-        <v>1.035</v>
+        <v>1.031</v>
       </c>
       <c r="E6">
-        <v>1.017</v>
+        <v>1.015</v>
       </c>
       <c r="F6">
         <v>0.032</v>
       </c>
       <c r="G6">
-        <v>59.858</v>
+        <v>58.992</v>
       </c>
       <c r="H6">
-        <v>63.846</v>
+        <v>62.972</v>
       </c>
       <c r="I6">
-        <v>59.866</v>
+        <v>59.001</v>
       </c>
       <c r="J6">
-        <v>63.838</v>
+        <v>63.032</v>
       </c>
       <c r="K6">
-        <v>59.825</v>
+        <v>58.875</v>
       </c>
       <c r="L6">
-        <v>63.797</v>
+        <v>62.906</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>49.495</v>
+        <v>49.667</v>
       </c>
       <c r="D7">
-        <v>0.852</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E7">
-        <v>0.923</v>
+        <v>0.968</v>
       </c>
       <c r="F7">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="G7">
-        <v>47.686</v>
+        <v>47.789</v>
       </c>
       <c r="H7">
-        <v>51.305</v>
+        <v>51.582</v>
       </c>
       <c r="I7">
-        <v>47.709</v>
+        <v>47.729</v>
       </c>
       <c r="J7">
-        <v>51.198</v>
+        <v>51.478</v>
       </c>
       <c r="K7">
-        <v>47.792</v>
+        <v>47.874</v>
       </c>
       <c r="L7">
-        <v>51.281</v>
+        <v>51.623</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>41.72</v>
+        <v>43.097</v>
       </c>
       <c r="D8">
-        <v>0.6889999999999999</v>
+        <v>0.872</v>
       </c>
       <c r="E8">
-        <v>0.83</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F8">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="G8">
-        <v>40.121</v>
+        <v>41.318</v>
       </c>
       <c r="H8">
-        <v>43.375</v>
+        <v>44.978</v>
       </c>
       <c r="I8">
-        <v>39.984</v>
+        <v>41.17</v>
       </c>
       <c r="J8">
-        <v>43.367</v>
+        <v>44.95</v>
       </c>
       <c r="K8">
-        <v>40.101</v>
+        <v>41.295</v>
       </c>
       <c r="L8">
-        <v>43.484</v>
+        <v>45.075</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>36.093</v>
+        <v>37.381</v>
       </c>
       <c r="D9">
-        <v>0.62</v>
+        <v>0.765</v>
       </c>
       <c r="E9">
-        <v>0.787</v>
+        <v>0.874</v>
       </c>
       <c r="F9">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
       <c r="G9">
-        <v>34.518</v>
+        <v>35.649</v>
       </c>
       <c r="H9">
-        <v>37.605</v>
+        <v>39.077</v>
       </c>
       <c r="I9">
-        <v>34.501</v>
+        <v>35.637</v>
       </c>
       <c r="J9">
-        <v>37.609</v>
+        <v>39.06</v>
       </c>
       <c r="K9">
-        <v>34.545</v>
+        <v>35.684</v>
       </c>
       <c r="L9">
-        <v>37.653</v>
+        <v>39.108</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>31.906</v>
+        <v>33.256</v>
       </c>
       <c r="D10">
-        <v>0.515</v>
+        <v>0.635</v>
       </c>
       <c r="E10">
-        <v>0.717</v>
+        <v>0.797</v>
       </c>
       <c r="F10">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="G10">
-        <v>30.493</v>
+        <v>31.68</v>
       </c>
       <c r="H10">
-        <v>33.304</v>
+        <v>34.804</v>
       </c>
       <c r="I10">
-        <v>30.457</v>
+        <v>31.669</v>
       </c>
       <c r="J10">
-        <v>33.273</v>
+        <v>34.772</v>
       </c>
       <c r="K10">
-        <v>30.531</v>
+        <v>31.725</v>
       </c>
       <c r="L10">
-        <v>33.347</v>
+        <v>34.829</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>30.717</v>
+        <v>32.251</v>
       </c>
       <c r="D11">
-        <v>0.47</v>
+        <v>0.575</v>
       </c>
       <c r="E11">
-        <v>0.6860000000000001</v>
+        <v>0.758</v>
       </c>
       <c r="F11">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="G11">
-        <v>29.361</v>
+        <v>30.752</v>
       </c>
       <c r="H11">
-        <v>32.048</v>
+        <v>33.724</v>
       </c>
       <c r="I11">
-        <v>29.308</v>
+        <v>30.745</v>
       </c>
       <c r="J11">
-        <v>32.022</v>
+        <v>33.706</v>
       </c>
       <c r="K11">
-        <v>29.399</v>
+        <v>30.783</v>
       </c>
       <c r="L11">
-        <v>32.113</v>
+        <v>33.744</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>28.684</v>
+        <v>29.884</v>
       </c>
       <c r="D12">
-        <v>0.574</v>
+        <v>0.635</v>
       </c>
       <c r="E12">
-        <v>0.758</v>
+        <v>0.797</v>
       </c>
       <c r="F12">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G12">
-        <v>27.122</v>
+        <v>28.235</v>
       </c>
       <c r="H12">
-        <v>30.092</v>
+        <v>31.358</v>
       </c>
       <c r="I12">
-        <v>27.069</v>
+        <v>28.168</v>
       </c>
       <c r="J12">
-        <v>30.071</v>
+        <v>31.272</v>
       </c>
       <c r="K12">
-        <v>27.22</v>
+        <v>28.409</v>
       </c>
       <c r="L12">
-        <v>30.221</v>
+        <v>31.512</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>29.37</v>
+        <v>30.825</v>
       </c>
       <c r="D13">
-        <v>0.512</v>
+        <v>0.58</v>
       </c>
       <c r="E13">
-        <v>0.715</v>
+        <v>0.762</v>
       </c>
       <c r="F13">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G13">
-        <v>27.929</v>
+        <v>29.295</v>
       </c>
       <c r="H13">
-        <v>30.733</v>
+        <v>32.28</v>
       </c>
       <c r="I13">
-        <v>27.844</v>
+        <v>29.254</v>
       </c>
       <c r="J13">
-        <v>30.729</v>
+        <v>32.219</v>
       </c>
       <c r="K13">
-        <v>27.972</v>
+        <v>29.394</v>
       </c>
       <c r="L13">
-        <v>30.857</v>
+        <v>32.359</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>25.117</v>
+        <v>26.358</v>
       </c>
       <c r="D14">
-        <v>0.365</v>
+        <v>0.443</v>
       </c>
       <c r="E14">
-        <v>0.604</v>
+        <v>0.665</v>
       </c>
       <c r="F14">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="G14">
-        <v>23.926</v>
+        <v>25.051</v>
       </c>
       <c r="H14">
-        <v>26.294</v>
+        <v>27.658</v>
       </c>
       <c r="I14">
-        <v>23.879</v>
+        <v>25.065</v>
       </c>
       <c r="J14">
-        <v>26.263</v>
+        <v>27.622</v>
       </c>
       <c r="K14">
-        <v>23.964</v>
+        <v>25.09</v>
       </c>
       <c r="L14">
-        <v>26.348</v>
+        <v>27.648</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
+        <v>26.437</v>
+      </c>
+      <c r="D15">
+        <v>0.464</v>
+      </c>
+      <c r="E15">
+        <v>0.681</v>
+      </c>
+      <c r="F15">
+        <v>0.022</v>
+      </c>
+      <c r="G15">
         <v>25.12</v>
       </c>
-      <c r="D15">
-        <v>0.395</v>
-      </c>
-      <c r="E15">
-        <v>0.629</v>
-      </c>
-      <c r="F15">
-        <v>0.02</v>
-      </c>
-      <c r="G15">
-        <v>23.895</v>
-      </c>
       <c r="H15">
-        <v>26.359</v>
+        <v>27.791</v>
       </c>
       <c r="I15">
-        <v>23.919</v>
+        <v>25.123</v>
       </c>
       <c r="J15">
-        <v>26.346</v>
+        <v>27.778</v>
       </c>
       <c r="K15">
-        <v>23.901</v>
+        <v>25.114</v>
       </c>
       <c r="L15">
-        <v>26.328</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>23.611</v>
+        <v>24.849</v>
       </c>
       <c r="D16">
-        <v>0.401</v>
+        <v>0.511</v>
       </c>
       <c r="E16">
-        <v>0.633</v>
+        <v>0.715</v>
       </c>
       <c r="F16">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="G16">
-        <v>22.313</v>
+        <v>23.395</v>
       </c>
       <c r="H16">
-        <v>24.794</v>
+        <v>26.198</v>
       </c>
       <c r="I16">
-        <v>22.264</v>
+        <v>23.378</v>
       </c>
       <c r="J16">
-        <v>24.77</v>
+        <v>26.167</v>
       </c>
       <c r="K16">
-        <v>22.395</v>
+        <v>23.479</v>
       </c>
       <c r="L16">
-        <v>24.9</v>
+        <v>26.268</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>23.72</v>
+        <v>24.524</v>
       </c>
       <c r="D17">
-        <v>0.437</v>
+        <v>0.457</v>
       </c>
       <c r="E17">
-        <v>0.661</v>
+        <v>0.676</v>
       </c>
       <c r="F17">
         <v>0.021</v>
       </c>
       <c r="G17">
-        <v>22.381</v>
+        <v>23.152</v>
       </c>
       <c r="H17">
-        <v>24.972</v>
+        <v>25.802</v>
       </c>
       <c r="I17">
-        <v>22.351</v>
+        <v>23.164</v>
       </c>
       <c r="J17">
-        <v>24.958</v>
+        <v>25.815</v>
       </c>
       <c r="K17">
-        <v>22.438</v>
+        <v>23.187</v>
       </c>
       <c r="L17">
-        <v>25.046</v>
+        <v>25.837</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>22.948</v>
+        <v>24.176</v>
       </c>
       <c r="D18">
-        <v>0.406</v>
+        <v>0.474</v>
       </c>
       <c r="E18">
-        <v>0.637</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F18">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="G18">
-        <v>21.682</v>
+        <v>22.811</v>
       </c>
       <c r="H18">
-        <v>24.178</v>
+        <v>25.511</v>
       </c>
       <c r="I18">
-        <v>21.596</v>
+        <v>22.774</v>
       </c>
       <c r="J18">
-        <v>24.141</v>
+        <v>25.452</v>
       </c>
       <c r="K18">
-        <v>21.737</v>
+        <v>22.886</v>
       </c>
       <c r="L18">
-        <v>24.281</v>
+        <v>25.563</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>21.272</v>
+        <v>22.247</v>
       </c>
       <c r="D19">
-        <v>0.377</v>
+        <v>0.416</v>
       </c>
       <c r="E19">
-        <v>0.614</v>
+        <v>0.645</v>
       </c>
       <c r="F19">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G19">
-        <v>20.011</v>
+        <v>20.941</v>
       </c>
       <c r="H19">
-        <v>22.416</v>
+        <v>23.468</v>
       </c>
       <c r="I19">
-        <v>19.983</v>
+        <v>20.922</v>
       </c>
       <c r="J19">
-        <v>22.42</v>
+        <v>23.448</v>
       </c>
       <c r="K19">
-        <v>20.065</v>
+        <v>21.003</v>
       </c>
       <c r="L19">
-        <v>22.502</v>
+        <v>23.529</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>20.571</v>
+        <v>21.708</v>
       </c>
       <c r="D20">
-        <v>0.339</v>
+        <v>0.575</v>
       </c>
       <c r="E20">
-        <v>0.582</v>
+        <v>0.759</v>
       </c>
       <c r="F20">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="G20">
-        <v>19.415</v>
+        <v>20.213</v>
       </c>
       <c r="H20">
-        <v>21.696</v>
+        <v>23.186</v>
       </c>
       <c r="I20">
-        <v>19.316</v>
+        <v>20.062</v>
       </c>
       <c r="J20">
-        <v>21.684</v>
+        <v>23.123</v>
       </c>
       <c r="K20">
-        <v>19.443</v>
+        <v>20.284</v>
       </c>
       <c r="L20">
-        <v>21.811</v>
+        <v>23.345</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>19.884</v>
+        <v>20.945</v>
       </c>
       <c r="D21">
-        <v>0.338</v>
+        <v>0.4</v>
       </c>
       <c r="E21">
-        <v>0.582</v>
+        <v>0.633</v>
       </c>
       <c r="F21">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="G21">
-        <v>18.681</v>
+        <v>19.639</v>
       </c>
       <c r="H21">
-        <v>20.961</v>
+        <v>22.118</v>
       </c>
       <c r="I21">
-        <v>18.6</v>
+        <v>19.588</v>
       </c>
       <c r="J21">
-        <v>20.963</v>
+        <v>22.087</v>
       </c>
       <c r="K21">
-        <v>18.742</v>
+        <v>19.736</v>
       </c>
       <c r="L21">
-        <v>21.105</v>
+        <v>22.236</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>19.223</v>
+        <v>20.077</v>
       </c>
       <c r="D22">
-        <v>0.368</v>
+        <v>0.432</v>
       </c>
       <c r="E22">
-        <v>0.606</v>
+        <v>0.657</v>
       </c>
       <c r="F22">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="G22">
-        <v>18.044</v>
+        <v>18.804</v>
       </c>
       <c r="H22">
-        <v>20.42</v>
+        <v>21.379</v>
       </c>
       <c r="I22">
-        <v>18.06</v>
+        <v>18.793</v>
       </c>
       <c r="J22">
-        <v>20.369</v>
+        <v>21.327</v>
       </c>
       <c r="K22">
-        <v>18.085</v>
+        <v>18.842</v>
       </c>
       <c r="L22">
-        <v>20.395</v>
+        <v>21.376</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>17.65</v>
+        <v>18.486</v>
       </c>
       <c r="D23">
-        <v>0.296</v>
+        <v>0.33</v>
       </c>
       <c r="E23">
-        <v>0.544</v>
+        <v>0.575</v>
       </c>
       <c r="F23">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="G23">
-        <v>16.611</v>
+        <v>17.397</v>
       </c>
       <c r="H23">
-        <v>18.745</v>
+        <v>19.649</v>
       </c>
       <c r="I23">
-        <v>16.595</v>
+        <v>17.352</v>
       </c>
       <c r="J23">
-        <v>18.777</v>
+        <v>19.636</v>
       </c>
       <c r="K23">
-        <v>16.55</v>
+        <v>17.374</v>
       </c>
       <c r="L23">
-        <v>18.732</v>
+        <v>19.658</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>17.5</v>
+        <v>18.184</v>
       </c>
       <c r="D24">
-        <v>0.35</v>
+        <v>0.379</v>
       </c>
       <c r="E24">
-        <v>0.591</v>
+        <v>0.616</v>
       </c>
       <c r="F24">
         <v>0.019</v>
       </c>
       <c r="G24">
-        <v>16.33</v>
+        <v>16.979</v>
       </c>
       <c r="H24">
-        <v>18.649</v>
+        <v>19.392</v>
       </c>
       <c r="I24">
-        <v>16.333</v>
+        <v>16.985</v>
       </c>
       <c r="J24">
-        <v>18.704</v>
+        <v>19.419</v>
       </c>
       <c r="K24">
-        <v>16.286</v>
+        <v>16.95</v>
       </c>
       <c r="L24">
-        <v>18.657</v>
+        <v>19.384</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>16.141</v>
+        <v>16.638</v>
       </c>
       <c r="D25">
-        <v>0.259</v>
+        <v>0.273</v>
       </c>
       <c r="E25">
-        <v>0.509</v>
+        <v>0.523</v>
       </c>
       <c r="F25">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="G25">
-        <v>15.139</v>
+        <v>15.596</v>
       </c>
       <c r="H25">
-        <v>17.136</v>
+        <v>17.646</v>
       </c>
       <c r="I25">
-        <v>15.065</v>
+        <v>15.553</v>
       </c>
       <c r="J25">
-        <v>17.08</v>
+        <v>17.602</v>
       </c>
       <c r="K25">
-        <v>15.199</v>
+        <v>15.657</v>
       </c>
       <c r="L25">
-        <v>17.214</v>
+        <v>17.706</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>257.074</v>
+        <v>274.55</v>
       </c>
       <c r="D26">
-        <v>5.839</v>
+        <v>6.707</v>
       </c>
       <c r="E26">
-        <v>2.416</v>
+        <v>2.59</v>
       </c>
       <c r="F26">
-        <v>0.076</v>
+        <v>0.082</v>
       </c>
       <c r="G26">
-        <v>252.456</v>
+        <v>269.546</v>
       </c>
       <c r="H26">
-        <v>261.928</v>
+        <v>279.698</v>
       </c>
       <c r="I26">
-        <v>252.289</v>
+        <v>269.594</v>
       </c>
       <c r="J26">
-        <v>261.758</v>
+        <v>279.535</v>
       </c>
       <c r="K26">
-        <v>252.508</v>
+        <v>269.637</v>
       </c>
       <c r="L26">
-        <v>261.977</v>
+        <v>279.578</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>182.884</v>
+        <v>185.38</v>
       </c>
       <c r="D27">
-        <v>3.958</v>
+        <v>4.157</v>
       </c>
       <c r="E27">
-        <v>1.989</v>
+        <v>2.039</v>
       </c>
       <c r="F27">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="G27">
-        <v>179.008</v>
+        <v>181.407</v>
       </c>
       <c r="H27">
-        <v>186.807</v>
+        <v>189.398</v>
       </c>
       <c r="I27">
-        <v>178.862</v>
+        <v>181.193</v>
       </c>
       <c r="J27">
-        <v>186.655</v>
+        <v>189.298</v>
       </c>
       <c r="K27">
-        <v>179.136</v>
+        <v>181.484</v>
       </c>
       <c r="L27">
-        <v>186.929</v>
+        <v>189.589</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>126.795</v>
+        <v>124.044</v>
       </c>
       <c r="D28">
-        <v>2.631</v>
+        <v>2.795</v>
       </c>
       <c r="E28">
-        <v>1.622</v>
+        <v>1.672</v>
       </c>
       <c r="F28">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="G28">
-        <v>123.661</v>
+        <v>120.816</v>
       </c>
       <c r="H28">
-        <v>130.019</v>
+        <v>127.369</v>
       </c>
       <c r="I28">
-        <v>123.529</v>
+        <v>120.555</v>
       </c>
       <c r="J28">
-        <v>129.943</v>
+        <v>127.327</v>
       </c>
       <c r="K28">
-        <v>123.692</v>
+        <v>120.811</v>
       </c>
       <c r="L28">
-        <v>130.107</v>
+        <v>127.583</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>90.12</v>
+        <v>88.208</v>
       </c>
       <c r="D29">
-        <v>3.175</v>
+        <v>3.292</v>
       </c>
       <c r="E29">
-        <v>1.782</v>
+        <v>1.814</v>
       </c>
       <c r="F29">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="G29">
-        <v>86.68000000000001</v>
+        <v>84.678</v>
       </c>
       <c r="H29">
-        <v>93.666</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="I29">
-        <v>86.289</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="J29">
-        <v>93.38800000000001</v>
+        <v>91.577</v>
       </c>
       <c r="K29">
-        <v>86.90600000000001</v>
+        <v>84.864</v>
       </c>
       <c r="L29">
-        <v>94.005</v>
+        <v>92.23099999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>69.002</v>
+        <v>68.027</v>
       </c>
       <c r="D30">
-        <v>1.329</v>
+        <v>1.345</v>
       </c>
       <c r="E30">
-        <v>1.153</v>
+        <v>1.16</v>
       </c>
       <c r="F30">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="G30">
-        <v>66.798</v>
+        <v>65.79900000000001</v>
       </c>
       <c r="H30">
-        <v>71.31699999999999</v>
+        <v>70.346</v>
       </c>
       <c r="I30">
-        <v>66.703</v>
+        <v>65.706</v>
       </c>
       <c r="J30">
-        <v>71.247</v>
+        <v>70.307</v>
       </c>
       <c r="K30">
-        <v>66.812</v>
+        <v>65.792</v>
       </c>
       <c r="L30">
-        <v>71.35599999999999</v>
+        <v>70.393</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>55.284</v>
+        <v>55.48</v>
       </c>
       <c r="D31">
-        <v>1.065</v>
+        <v>1.157</v>
       </c>
       <c r="E31">
-        <v>1.032</v>
+        <v>1.076</v>
       </c>
       <c r="F31">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="G31">
-        <v>53.209</v>
+        <v>53.331</v>
       </c>
       <c r="H31">
-        <v>57.254</v>
+        <v>57.548</v>
       </c>
       <c r="I31">
-        <v>53.149</v>
+        <v>53.27</v>
       </c>
       <c r="J31">
-        <v>57.223</v>
+        <v>57.482</v>
       </c>
       <c r="K31">
-        <v>53.292</v>
+        <v>53.437</v>
       </c>
       <c r="L31">
-        <v>57.366</v>
+        <v>57.649</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>46.587</v>
+        <v>48.142</v>
       </c>
       <c r="D32">
-        <v>0.907</v>
+        <v>1.127</v>
       </c>
       <c r="E32">
-        <v>0.952</v>
+        <v>1.062</v>
       </c>
       <c r="F32">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="G32">
-        <v>44.732</v>
+        <v>46.063</v>
       </c>
       <c r="H32">
-        <v>48.466</v>
+        <v>50.224</v>
       </c>
       <c r="I32">
-        <v>44.667</v>
+        <v>46.006</v>
       </c>
       <c r="J32">
-        <v>48.457</v>
+        <v>50.251</v>
       </c>
       <c r="K32">
-        <v>44.729</v>
+        <v>46.034</v>
       </c>
       <c r="L32">
-        <v>48.518</v>
+        <v>50.28</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>40.314</v>
+        <v>41.76</v>
       </c>
       <c r="D33">
-        <v>0.759</v>
+        <v>0.915</v>
       </c>
       <c r="E33">
-        <v>0.871</v>
+        <v>0.956</v>
       </c>
       <c r="F33">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="G33">
-        <v>38.532</v>
+        <v>39.811</v>
       </c>
       <c r="H33">
-        <v>41.948</v>
+        <v>43.56</v>
       </c>
       <c r="I33">
-        <v>38.577</v>
+        <v>39.79</v>
       </c>
       <c r="J33">
-        <v>42.03</v>
+        <v>43.658</v>
       </c>
       <c r="K33">
-        <v>38.525</v>
+        <v>39.788</v>
       </c>
       <c r="L33">
-        <v>41.977</v>
+        <v>43.656</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>35.655</v>
+        <v>37.154</v>
       </c>
       <c r="D34">
-        <v>0.586</v>
+        <v>0.7</v>
       </c>
       <c r="E34">
-        <v>0.765</v>
+        <v>0.837</v>
       </c>
       <c r="F34">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="G34">
-        <v>34.077</v>
+        <v>35.446</v>
       </c>
       <c r="H34">
-        <v>37.077</v>
+        <v>38.725</v>
       </c>
       <c r="I34">
-        <v>34.023</v>
+        <v>35.424</v>
       </c>
       <c r="J34">
-        <v>37.077</v>
+        <v>38.701</v>
       </c>
       <c r="K34">
-        <v>34.156</v>
+        <v>35.539</v>
       </c>
       <c r="L34">
-        <v>37.21</v>
+        <v>38.816</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>34.306</v>
+        <v>36.018</v>
       </c>
       <c r="D35">
-        <v>0.5669999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E35">
-        <v>0.753</v>
+        <v>0.83</v>
       </c>
       <c r="F35">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="G35">
-        <v>32.789</v>
+        <v>34.352</v>
       </c>
       <c r="H35">
-        <v>35.742</v>
+        <v>37.605</v>
       </c>
       <c r="I35">
-        <v>32.705</v>
+        <v>34.22</v>
       </c>
       <c r="J35">
-        <v>35.782</v>
+        <v>37.645</v>
       </c>
       <c r="K35">
-        <v>32.79</v>
+        <v>34.352</v>
       </c>
       <c r="L35">
-        <v>35.867</v>
+        <v>37.777</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>31.949</v>
+        <v>33.278</v>
       </c>
       <c r="D36">
-        <v>0.644</v>
+        <v>0.719</v>
       </c>
       <c r="E36">
-        <v>0.802</v>
+        <v>0.848</v>
       </c>
       <c r="F36">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="G36">
-        <v>30.439</v>
+        <v>31.688</v>
       </c>
       <c r="H36">
-        <v>33.583</v>
+        <v>35.013</v>
       </c>
       <c r="I36">
-        <v>30.442</v>
+        <v>31.618</v>
       </c>
       <c r="J36">
-        <v>33.447</v>
+        <v>34.949</v>
       </c>
       <c r="K36">
-        <v>30.513</v>
+        <v>31.679</v>
       </c>
       <c r="L36">
-        <v>33.518</v>
+        <v>35.01</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>32.762</v>
+        <v>34.389</v>
       </c>
       <c r="D37">
-        <v>0.569</v>
+        <v>0.661</v>
       </c>
       <c r="E37">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F37">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="G37">
-        <v>31.295</v>
+        <v>32.803</v>
       </c>
       <c r="H37">
-        <v>34.252</v>
+        <v>35.99</v>
       </c>
       <c r="I37">
-        <v>31.313</v>
+        <v>32.757</v>
       </c>
       <c r="J37">
-        <v>34.205</v>
+        <v>35.922</v>
       </c>
       <c r="K37">
-        <v>31.33</v>
+        <v>32.864</v>
       </c>
       <c r="L37">
-        <v>34.222</v>
+        <v>36.029</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>28.061</v>
+        <v>29.451</v>
       </c>
       <c r="D38">
-        <v>0.446</v>
+        <v>0.535</v>
       </c>
       <c r="E38">
-        <v>0.668</v>
+        <v>0.732</v>
       </c>
       <c r="F38">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="G38">
-        <v>26.704</v>
+        <v>27.964</v>
       </c>
       <c r="H38">
-        <v>29.323</v>
+        <v>30.831</v>
       </c>
       <c r="I38">
-        <v>26.648</v>
+        <v>27.84</v>
       </c>
       <c r="J38">
-        <v>29.319</v>
+        <v>30.815</v>
       </c>
       <c r="K38">
-        <v>26.755</v>
+        <v>28.034</v>
       </c>
       <c r="L38">
-        <v>29.426</v>
+        <v>31.009</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>28.06</v>
+        <v>29.542</v>
       </c>
       <c r="D39">
-        <v>0.439</v>
+        <v>0.52</v>
       </c>
       <c r="E39">
-        <v>0.663</v>
+        <v>0.721</v>
       </c>
       <c r="F39">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="G39">
-        <v>26.738</v>
+        <v>28.095</v>
       </c>
       <c r="H39">
-        <v>29.336</v>
+        <v>30.922</v>
       </c>
       <c r="I39">
-        <v>26.755</v>
+        <v>28.014</v>
       </c>
       <c r="J39">
-        <v>29.343</v>
+        <v>30.933</v>
       </c>
       <c r="K39">
-        <v>26.754</v>
+        <v>28.117</v>
       </c>
       <c r="L39">
-        <v>29.342</v>
+        <v>31.036</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>26.325</v>
+        <v>27.714</v>
       </c>
       <c r="D40">
-        <v>0.445</v>
+        <v>0.577</v>
       </c>
       <c r="E40">
-        <v>0.667</v>
+        <v>0.759</v>
       </c>
       <c r="F40">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="G40">
-        <v>25.023</v>
+        <v>26.223</v>
       </c>
       <c r="H40">
-        <v>27.638</v>
+        <v>29.199</v>
       </c>
       <c r="I40">
-        <v>24.964</v>
+        <v>26.157</v>
       </c>
       <c r="J40">
-        <v>27.586</v>
+        <v>29.134</v>
       </c>
       <c r="K40">
-        <v>25.07</v>
+        <v>26.292</v>
       </c>
       <c r="L40">
-        <v>27.691</v>
+        <v>29.269</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>26.472</v>
+        <v>27.36</v>
       </c>
       <c r="D41">
-        <v>0.552</v>
+        <v>0.576</v>
       </c>
       <c r="E41">
-        <v>0.743</v>
+        <v>0.759</v>
       </c>
       <c r="F41">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="G41">
-        <v>24.986</v>
+        <v>25.859</v>
       </c>
       <c r="H41">
-        <v>27.899</v>
+        <v>28.833</v>
       </c>
       <c r="I41">
-        <v>24.974</v>
+        <v>25.874</v>
       </c>
       <c r="J41">
-        <v>27.802</v>
+        <v>28.769</v>
       </c>
       <c r="K41">
-        <v>25.113</v>
+        <v>25.937</v>
       </c>
       <c r="L41">
-        <v>27.94</v>
+        <v>28.832</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>25.621</v>
+        <v>26.996</v>
       </c>
       <c r="D42">
-        <v>0.495</v>
+        <v>0.575</v>
       </c>
       <c r="E42">
-        <v>0.703</v>
+        <v>0.758</v>
       </c>
       <c r="F42">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="G42">
-        <v>24.219</v>
+        <v>25.482</v>
       </c>
       <c r="H42">
-        <v>26.976</v>
+        <v>28.455</v>
       </c>
       <c r="I42">
-        <v>24.181</v>
+        <v>25.433</v>
       </c>
       <c r="J42">
-        <v>26.95</v>
+        <v>28.378</v>
       </c>
       <c r="K42">
-        <v>24.268</v>
+        <v>25.587</v>
       </c>
       <c r="L42">
-        <v>27.038</v>
+        <v>28.532</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>23.696</v>
+        <v>24.788</v>
       </c>
       <c r="D43">
-        <v>0.448</v>
+        <v>0.502</v>
       </c>
       <c r="E43">
-        <v>0.669</v>
+        <v>0.709</v>
       </c>
       <c r="F43">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G43">
-        <v>22.424</v>
+        <v>23.449</v>
       </c>
       <c r="H43">
-        <v>25.048</v>
+        <v>26.227</v>
       </c>
       <c r="I43">
-        <v>22.308</v>
+        <v>23.33</v>
       </c>
       <c r="J43">
-        <v>24.973</v>
+        <v>26.192</v>
       </c>
       <c r="K43">
-        <v>22.459</v>
+        <v>23.434</v>
       </c>
       <c r="L43">
-        <v>25.124</v>
+        <v>26.296</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>22.951</v>
+        <v>24.211</v>
       </c>
       <c r="D44">
-        <v>0.45</v>
+        <v>0.768</v>
       </c>
       <c r="E44">
-        <v>0.671</v>
+        <v>0.876</v>
       </c>
       <c r="F44">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="G44">
-        <v>21.649</v>
+        <v>22.532</v>
       </c>
       <c r="H44">
-        <v>24.278</v>
+        <v>25.967</v>
       </c>
       <c r="I44">
-        <v>21.644</v>
+        <v>22.337</v>
       </c>
       <c r="J44">
-        <v>24.231</v>
+        <v>25.83</v>
       </c>
       <c r="K44">
-        <v>21.684</v>
+        <v>22.631</v>
       </c>
       <c r="L44">
-        <v>24.271</v>
+        <v>26.124</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>22.178</v>
+        <v>23.368</v>
       </c>
       <c r="D45">
-        <v>0.404</v>
+        <v>0.481</v>
       </c>
       <c r="E45">
-        <v>0.636</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F45">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="G45">
-        <v>20.903</v>
+        <v>21.966</v>
       </c>
       <c r="H45">
-        <v>23.396</v>
+        <v>24.684</v>
       </c>
       <c r="I45">
-        <v>20.858</v>
+        <v>21.942</v>
       </c>
       <c r="J45">
-        <v>23.355</v>
+        <v>24.65</v>
       </c>
       <c r="K45">
-        <v>20.973</v>
+        <v>22.042</v>
       </c>
       <c r="L45">
-        <v>23.47</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>21.467</v>
+        <v>22.432</v>
       </c>
       <c r="D46">
-        <v>0.427</v>
+        <v>0.502</v>
       </c>
       <c r="E46">
-        <v>0.653</v>
+        <v>0.708</v>
       </c>
       <c r="F46">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="G46">
-        <v>20.185</v>
+        <v>21.025</v>
       </c>
       <c r="H46">
-        <v>22.745</v>
+        <v>23.802</v>
       </c>
       <c r="I46">
-        <v>20.091</v>
+        <v>20.92</v>
       </c>
       <c r="J46">
-        <v>22.752</v>
+        <v>23.763</v>
       </c>
       <c r="K46">
-        <v>20.18</v>
+        <v>21.082</v>
       </c>
       <c r="L46">
-        <v>22.841</v>
+        <v>23.926</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>19.707</v>
+        <v>20.65</v>
       </c>
       <c r="D47">
-        <v>0.36</v>
+        <v>0.398</v>
       </c>
       <c r="E47">
-        <v>0.6</v>
+        <v>0.631</v>
       </c>
       <c r="F47">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="G47">
-        <v>18.557</v>
+        <v>19.431</v>
       </c>
       <c r="H47">
-        <v>20.91</v>
+        <v>21.905</v>
       </c>
       <c r="I47">
-        <v>18.512</v>
+        <v>19.371</v>
       </c>
       <c r="J47">
-        <v>20.886</v>
+        <v>21.885</v>
       </c>
       <c r="K47">
-        <v>18.555</v>
+        <v>19.433</v>
       </c>
       <c r="L47">
-        <v>20.929</v>
+        <v>21.947</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>19.552</v>
+        <v>20.328</v>
       </c>
       <c r="D48">
-        <v>0.414</v>
+        <v>0.452</v>
       </c>
       <c r="E48">
-        <v>0.643</v>
+        <v>0.672</v>
       </c>
       <c r="F48">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="G48">
-        <v>18.251</v>
+        <v>18.958</v>
       </c>
       <c r="H48">
-        <v>20.772</v>
+        <v>21.593</v>
       </c>
       <c r="I48">
-        <v>18.227</v>
+        <v>18.959</v>
       </c>
       <c r="J48">
-        <v>20.757</v>
+        <v>21.626</v>
       </c>
       <c r="K48">
-        <v>18.306</v>
+        <v>18.977</v>
       </c>
       <c r="L48">
-        <v>20.836</v>
+        <v>21.644</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>18.022</v>
+        <v>18.574</v>
       </c>
       <c r="D49">
-        <v>0.331</v>
+        <v>0.358</v>
       </c>
       <c r="E49">
-        <v>0.576</v>
+        <v>0.599</v>
       </c>
       <c r="F49">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="G49">
-        <v>16.887</v>
+        <v>17.384</v>
       </c>
       <c r="H49">
-        <v>19.143</v>
+        <v>19.731</v>
       </c>
       <c r="I49">
-        <v>16.935</v>
+        <v>17.405</v>
       </c>
       <c r="J49">
-        <v>19.099</v>
+        <v>19.665</v>
       </c>
       <c r="K49">
-        <v>16.938</v>
+        <v>17.466</v>
       </c>
       <c r="L49">
-        <v>19.102</v>
+        <v>19.726</v>
       </c>
     </row>
   </sheetData>
